--- a/docs/JMeter_Usage_Guide.xlsx
+++ b/docs/JMeter_Usage_Guide.xlsx
@@ -23,12 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="1052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="1059">
   <si>
     <t>JMeter APIテスト 利用方法</t>
   </si>
   <si>
-    <t>対象: Apache JMeter 5.6.3 ／ RHEL 9.8 ／ Windows 11 ／ ツール: jmeter_api_tool v1.0.0（2026-10-11 出力）</t>
+    <t>対象: Apache JMeter 5.6.3 ／ RHEL 9.8 ／ Windows 11 ／ ツール: jmeter_api_tool v1.0.0（2026-10-24 出力）</t>
   </si>
   <si>
     <t>本書は、REST API の定義（URL・HTTPメソッド・クエリパラメータ・ヘッダ・リクエストボディ）を Excel または CSV に記入し、JMeter のテスト計画ファイル（JMX）を自動生成して実行し、結果を確認するまでの手順をまとめたものです。</t>
@@ -782,6 +782,27 @@
   </si>
   <si>
     <t>全 API に付けるヘッダ。「名前: 値」を改行区切り（テンプレートの記入例: Accept: application/json / User-Agent: JMeter-API-Test/1.0 / X-Client-Id: ${CLIENT_ID}）</t>
+  </si>
+  <si>
+    <t>access_token_dir</t>
+  </si>
+  <si>
+    <t>アクセストークンのフォルダ</t>
+  </si>
+  <si>
+    <t>指定すると、このフォルダ配下のファイルからアクセストークンを読み込み、共通ヘッダに Authorization: Bearer ${ACCESS_TOKEN} を付けます（共通ヘッダに Authorization がある場合はその値を使用）。空欄 = 使わない。JMX からの相対パスまたは絶対パス。-JACCESS_TOKEN_DIR</t>
+  </si>
+  <si>
+    <t>access_token_file</t>
+  </si>
+  <si>
+    <t>アクセストークンのファイル名</t>
+  </si>
+  <si>
+    <t>access_token.txt</t>
+  </si>
+  <si>
+    <t>アクセストークンを書いたファイルの名前（フォルダからの相対パス）。前後の空白・改行は除き、実行中にファイルが更新されると読み直します。-JACCESS_TOKEN_FILE</t>
   </si>
   <si>
     <t>follow_redirects</t>
@@ -3800,50 +3821,50 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="C3" s="4"/>
     </row>
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="16.2" customHeight="1">
       <c r="B5" s="9" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="C5" s="9"/>
     </row>
     <row r="6" ht="16.2" customHeight="1">
       <c r="B6" s="10" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" ht="16.2" customHeight="1">
       <c r="B7" s="10" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" ht="16.2" customHeight="1">
       <c r="B8" s="10" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" ht="16.2" customHeight="1">
       <c r="B9" s="10" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" ht="16.2" customHeight="1">
       <c r="B10" s="10" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="C10" s="10"/>
     </row>
     <row r="11" ht="16.2" customHeight="1">
       <c r="B11" s="11" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -3851,55 +3872,55 @@
     <row r="13" ht="8" customHeight="1"/>
     <row r="14" ht="24" customHeight="1">
       <c r="B14" s="4" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15" ht="4" customHeight="1"/>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="13" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
     </row>
     <row r="17" ht="32.4" customHeight="1">
       <c r="B17" s="14" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="15" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="14" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
     </row>
     <row r="21" ht="6" customHeight="1"/>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="6" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="C22" s="6"/>
     </row>
@@ -3907,14 +3928,14 @@
     <row r="24" ht="8" customHeight="1"/>
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="4" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="C25" s="4"/>
     </row>
     <row r="26" ht="4" customHeight="1"/>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="13" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>6</v>
@@ -3922,104 +3943,104 @@
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="14" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="14" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
     </row>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="15" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="14" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="15" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="14" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="15" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="14" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="15" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="14" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
     </row>
     <row r="39" ht="6" customHeight="1"/>
     <row r="40" ht="8" customHeight="1"/>
     <row r="41" ht="24" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="C41" s="4"/>
     </row>
     <row r="42" ht="4" customHeight="1"/>
     <row r="43" ht="46.8" customHeight="1">
       <c r="B43" s="6" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="C43" s="6"/>
     </row>
@@ -4027,14 +4048,14 @@
     <row r="45" ht="8" customHeight="1"/>
     <row r="46" ht="24" customHeight="1">
       <c r="B46" s="4" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="C46" s="4"/>
     </row>
     <row r="47" ht="4" customHeight="1"/>
     <row r="48" ht="32.4" customHeight="1">
       <c r="B48" s="6" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="C48" s="6"/>
     </row>
@@ -4042,26 +4063,26 @@
     <row r="50" ht="8" customHeight="1"/>
     <row r="51" ht="24" customHeight="1">
       <c r="B51" s="4" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="C51" s="4"/>
     </row>
     <row r="52" ht="4" customHeight="1"/>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="7" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="C53" s="7"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="7" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="C54" s="7"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="7" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="C55" s="7"/>
     </row>
@@ -4121,7 +4142,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -4129,10 +4150,10 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>6</v>
@@ -4140,97 +4161,97 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="15" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
     </row>
     <row r="14" ht="6" customHeight="1"/>
     <row r="15" ht="8" customHeight="1"/>
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="4" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -4238,152 +4259,152 @@
     <row r="17" ht="4" customHeight="1"/>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="13" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="14" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="14" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="15" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="14" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="15" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="14" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="15" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="14" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="15" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="14" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="15" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
     </row>
     <row r="31" ht="6" customHeight="1"/>
     <row r="32" ht="8" customHeight="1"/>
     <row r="33" ht="24" customHeight="1">
       <c r="B33" s="4" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -4391,21 +4412,21 @@
     <row r="34" ht="4" customHeight="1"/>
     <row r="35" ht="16.2" customHeight="1">
       <c r="B35" s="9" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
     </row>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="10" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
@@ -4419,21 +4440,21 @@
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="10" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="16.2" customHeight="1">
       <c r="B41" s="10" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
@@ -4447,28 +4468,28 @@
     </row>
     <row r="43" ht="16.2" customHeight="1">
       <c r="B43" s="10" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
     </row>
     <row r="44" ht="16.2" customHeight="1">
       <c r="B44" s="10" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
     </row>
     <row r="45" ht="16.2" customHeight="1">
       <c r="B45" s="10" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
     </row>
     <row r="46" ht="16.2" customHeight="1">
       <c r="B46" s="10" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="C46" s="10"/>
       <c r="D46" s="10"/>
@@ -4482,14 +4503,14 @@
     </row>
     <row r="48" ht="16.2" customHeight="1">
       <c r="B48" s="10" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="10"/>
     </row>
     <row r="49" ht="16.2" customHeight="1">
       <c r="B49" s="11" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
@@ -4497,21 +4518,21 @@
     <row r="50" ht="6" customHeight="1"/>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="7" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="7" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="7" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -4520,7 +4541,7 @@
     <row r="55" ht="8" customHeight="1"/>
     <row r="56" ht="24" customHeight="1">
       <c r="B56" s="4" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
@@ -4528,60 +4549,60 @@
     <row r="57" ht="4" customHeight="1"/>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="13" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="D58" s="13"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="14" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="D59" s="14"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="15" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="D60" s="15"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="14" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="D61" s="14"/>
     </row>
     <row r="62" ht="32.4" customHeight="1">
       <c r="B62" s="15" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="D62" s="15"/>
     </row>
     <row r="63" ht="6" customHeight="1"/>
     <row r="64" ht="18" customHeight="1">
       <c r="B64" s="7" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="B65" s="7" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -4590,7 +4611,7 @@
     <row r="67" ht="8" customHeight="1"/>
     <row r="68" ht="24" customHeight="1">
       <c r="B68" s="4" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
@@ -4598,55 +4619,55 @@
     <row r="69" ht="4" customHeight="1"/>
     <row r="70" ht="18" customHeight="1">
       <c r="B70" s="13" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="D70" s="13"/>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="B71" s="14" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="D71" s="14"/>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="B72" s="15" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="D72" s="15"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="B73" s="14" t="s">
-        <v>938</v>
+        <v>945</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
       <c r="D73" s="14"/>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="B74" s="15" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>941</v>
+        <v>948</v>
       </c>
       <c r="D74" s="15"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="B75" s="14" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="D75" s="14"/>
     </row>
@@ -4723,200 +4744,200 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="13" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>945</v>
+        <v>952</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>946</v>
+        <v>953</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="B4" s="14" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>948</v>
+        <v>955</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="15" t="s">
-        <v>950</v>
+        <v>957</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
     </row>
     <row r="6" ht="32.4" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
     </row>
     <row r="7" ht="32.4" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
     </row>
     <row r="8" ht="32.4" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
     </row>
     <row r="10" ht="32.4" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
     </row>
     <row r="11" ht="32.4" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
     </row>
     <row r="13" ht="32.4" customHeight="1">
       <c r="B13" s="15" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
     </row>
     <row r="14" ht="32.4" customHeight="1">
       <c r="B14" s="14" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
     </row>
     <row r="15" ht="32.4" customHeight="1">
       <c r="B15" s="15" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
     </row>
     <row r="16" ht="32.4" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
     </row>
     <row r="17" ht="32.4" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
     </row>
     <row r="19" ht="32.4" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>992</v>
+        <v>999</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>993</v>
+        <v>1000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="20" ht="32.4" customHeight="1">
       <c r="B20" s="14" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="21" ht="6" customHeight="1"/>
@@ -4958,7 +4979,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>998</v>
+        <v>1005</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -4967,13 +4988,13 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>161</v>
@@ -4981,79 +5002,79 @@
     </row>
     <row r="6" ht="32.4" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1003</v>
+        <v>1010</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="7" ht="32.4" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="8" ht="32.4" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>1010</v>
+        <v>1017</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>134</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="11" ht="6" customHeight="1"/>
     <row r="12" ht="8" customHeight="1"/>
     <row r="13" ht="24" customHeight="1">
       <c r="B13" s="4" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -5062,7 +5083,7 @@
     <row r="14" ht="4" customHeight="1"/>
     <row r="15" ht="18" customHeight="1">
       <c r="B15" s="13" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>161</v>
@@ -5072,50 +5093,50 @@
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>1023</v>
+        <v>1030</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>1024</v>
+        <v>1031</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1025</v>
+        <v>1032</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1027</v>
+        <v>1034</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>1028</v>
+        <v>1035</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1029</v>
+        <v>1036</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="14" t="s">
-        <v>1030</v>
+        <v>1037</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1031</v>
+        <v>1038</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
@@ -5125,7 +5146,7 @@
         <v>168</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
@@ -5135,97 +5156,97 @@
         <v>174</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>1033</v>
+        <v>1040</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="15" t="s">
-        <v>1034</v>
+        <v>1041</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="14" t="s">
-        <v>1036</v>
+        <v>1043</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>1037</v>
+        <v>1044</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="15" t="s">
-        <v>1038</v>
+        <v>1045</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>1039</v>
+        <v>1046</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="14" t="s">
-        <v>1040</v>
+        <v>1047</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>1041</v>
+        <v>1048</v>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="15" t="s">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>1043</v>
+        <v>1050</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="14" t="s">
-        <v>1044</v>
+        <v>1051</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>1046</v>
+        <v>1053</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="14" t="s">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="15" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>1051</v>
+        <v>1058</v>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="15"/>
@@ -6368,7 +6389,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -6690,7 +6711,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
+    <row r="24" ht="61.2" customHeight="1">
       <c r="B24" s="15" t="s">
         <v>237</v>
       </c>
@@ -6701,24 +6722,24 @@
         <v>254</v>
       </c>
       <c r="E24" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="F24" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="F24" s="15" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
+    </row>
+    <row r="25" ht="46.8" customHeight="1">
       <c r="B25" s="14" t="s">
         <v>237</v>
       </c>
       <c r="C25" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="D25" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="E25" s="14" t="s">
         <v>258</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>255</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>259</v>
@@ -6743,75 +6764,75 @@
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="D27" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="E27" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="F27" s="14" t="s">
         <v>266</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="15" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="C28" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="D28" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="E28" s="15" t="s">
         <v>269</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>255</v>
       </c>
       <c r="F28" s="15" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="29" ht="32.4" customHeight="1">
+    <row r="29" ht="18" customHeight="1">
       <c r="B29" s="14" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="15" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>206</v>
+        <v>262</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="14" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>278</v>
@@ -6828,7 +6849,7 @@
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="15" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>281</v>
@@ -6837,24 +6858,24 @@
         <v>282</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="F32" s="15" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
+    <row r="33" ht="32.4" customHeight="1">
       <c r="B33" s="14" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>286</v>
+        <v>206</v>
       </c>
       <c r="F33" s="14" t="s">
         <v>287</v>
@@ -6862,7 +6883,7 @@
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="15" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>288</v>
@@ -6871,71 +6892,71 @@
         <v>289</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" s="15"/>
+        <v>240</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="14" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" s="14"/>
+        <v>293</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="15" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>295</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F36" s="15"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="14" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="F37" s="14" t="s">
-        <v>299</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F37" s="14"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="15" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C38" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="D38" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="E38" s="15" t="s">
         <v>301</v>
-      </c>
-      <c r="E38" s="15" t="s">
-        <v>240</v>
       </c>
       <c r="F38" s="15" t="s">
         <v>302</v>
@@ -6943,7 +6964,7 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="14" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>303</v>
@@ -6954,58 +6975,60 @@
       <c r="E39" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="F39" s="14"/>
+      <c r="F39" s="14" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="15" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" s="15"/>
+        <v>240</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="14" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F41" s="14"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="15" t="s">
-        <v>311</v>
+        <v>284</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="43" ht="32.4" customHeight="1">
+        <v>7</v>
+      </c>
+      <c r="F42" s="15"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
       <c r="B43" s="14" t="s">
-        <v>311</v>
+        <v>284</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>315</v>
@@ -7016,13 +7039,11 @@
       <c r="E43" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="F43" s="14" t="s">
-        <v>318</v>
-      </c>
+      <c r="F43" s="14"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="15" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>319</v>
@@ -7031,15 +7052,15 @@
         <v>320</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="F44" s="15" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="45" ht="18" customHeight="1">
+    <row r="45" ht="32.4" customHeight="1">
       <c r="B45" s="14" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>322</v>
@@ -7048,71 +7069,71 @@
         <v>323</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="F45" s="14"/>
+        <v>324</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="15" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>326</v>
-      </c>
-      <c r="F46" s="15"/>
+        <v>206</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="14" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="F47" s="14" t="s">
-        <v>329</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="F47" s="14"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="15" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="F48" s="15" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="49" ht="32.4" customHeight="1">
+        <v>333</v>
+      </c>
+      <c r="F48" s="15"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
       <c r="B49" s="14" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>335</v>
+        <v>262</v>
       </c>
       <c r="F49" s="14" t="s">
         <v>336</v>
@@ -7120,41 +7141,41 @@
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="C50" s="15" t="s">
         <v>337</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="D50" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="D50" s="15" t="s">
+      <c r="E50" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="F50" s="15" t="s">
         <v>339</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="F50" s="15" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="51" ht="32.4" customHeight="1">
       <c r="B51" s="14" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="C51" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="D51" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="E51" s="14" t="s">
         <v>342</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="F51" s="14" t="s">
         <v>343</v>
-      </c>
-      <c r="F51" s="14" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="15" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>345</v>
@@ -7163,32 +7184,32 @@
         <v>346</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
+    <row r="53" ht="32.4" customHeight="1">
       <c r="B53" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="C53" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="D53" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="E53" s="14" t="s">
         <v>350</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>240</v>
       </c>
       <c r="F53" s="14" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="54" ht="32.4" customHeight="1">
+    <row r="54" ht="18" customHeight="1">
       <c r="B54" s="15" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C54" s="15" t="s">
         <v>352</v>
@@ -7197,32 +7218,32 @@
         <v>353</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="F54" s="15" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="55" ht="32.4" customHeight="1">
+    <row r="55" ht="18" customHeight="1">
       <c r="B55" s="14" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>240</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="56" ht="32.4" customHeight="1">
       <c r="B56" s="15" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>359</v>
@@ -7231,32 +7252,32 @@
         <v>360</v>
       </c>
       <c r="E56" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="F56" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="F56" s="15" t="s">
+    </row>
+    <row r="57" ht="32.4" customHeight="1">
+      <c r="B57" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="C57" s="14" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="B57" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="C57" s="14" t="s">
+      <c r="D57" s="14" t="s">
         <v>363</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>364</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>240</v>
       </c>
       <c r="F57" s="14" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="58" ht="32.4" customHeight="1">
+      <c r="B58" s="15" t="s">
         <v>365</v>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="B58" s="15" t="s">
-        <v>358</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>366</v>
@@ -7265,92 +7286,92 @@
         <v>367</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>240</v>
+        <v>368</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="14" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>240</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="15" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E60" s="15" t="s">
         <v>240</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="14" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E61" s="14" t="s">
         <v>240</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="B62" s="15" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E62" s="15" t="s">
         <v>240</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="B63" s="14" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>383</v>
+        <v>240</v>
       </c>
       <c r="F63" s="14" t="s">
         <v>384</v>
@@ -7358,7 +7379,7 @@
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="B64" s="15" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C64" s="15" t="s">
         <v>385</v>
@@ -7367,30 +7388,64 @@
         <v>386</v>
       </c>
       <c r="E64" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="F64" s="15" t="s">
         <v>387</v>
-      </c>
-      <c r="F64" s="15" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="B65" s="14" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C65" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="D65" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="E65" s="14" t="s">
         <v>390</v>
-      </c>
-      <c r="E65" s="14" t="s">
-        <v>231</v>
       </c>
       <c r="F65" s="14" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="66" ht="6" customHeight="1"/>
+    <row r="66" ht="18" customHeight="1">
+      <c r="B66" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="F66" s="15" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="B67" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="E67" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="F67" s="14" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="68" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B1:F1"/>
@@ -7432,7 +7487,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -7441,16 +7496,16 @@
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>161</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" ht="32.4" customHeight="1">
@@ -7459,7 +7514,7 @@
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>7</v>
@@ -7467,198 +7522,198 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10" ht="32.4" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" ht="32.4" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="15" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="14" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15" ht="32.4" customHeight="1">
       <c r="B15" s="15" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16" ht="32.4" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="14" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="14" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="15" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="14" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="15" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22" ht="32.4" customHeight="1">
       <c r="B22" s="14" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -7667,7 +7722,7 @@
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="E23" s="15"/>
     </row>
@@ -7675,7 +7730,7 @@
     <row r="25" ht="8" customHeight="1"/>
     <row r="26" ht="24" customHeight="1">
       <c r="B26" s="4" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -7684,7 +7739,7 @@
     <row r="27" ht="4" customHeight="1"/>
     <row r="28" ht="32.4" customHeight="1">
       <c r="B28" s="7" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -7692,7 +7747,7 @@
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="7" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -7700,7 +7755,7 @@
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="7" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -7708,7 +7763,7 @@
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="7" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -7716,7 +7771,7 @@
     </row>
     <row r="32" ht="32.4" customHeight="1">
       <c r="B32" s="7" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -7724,7 +7779,7 @@
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="7" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -7732,7 +7787,7 @@
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="7" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -7742,7 +7797,7 @@
     <row r="36" ht="8" customHeight="1"/>
     <row r="37" ht="24" customHeight="1">
       <c r="B37" s="4" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -7751,61 +7806,61 @@
     <row r="38" ht="4" customHeight="1"/>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="13" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="E39" s="13"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="14" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="E40" s="14"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="15" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="E41" s="15"/>
     </row>
     <row r="42" ht="32.4" customHeight="1">
       <c r="B42" s="14" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="E42" s="14"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="15" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="E43" s="15"/>
     </row>
@@ -7863,7 +7918,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -7872,7 +7927,7 @@
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="16.2" customHeight="1">
       <c r="B5" s="9" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -7880,7 +7935,7 @@
     </row>
     <row r="6" ht="16.2" customHeight="1">
       <c r="B6" s="10" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -7888,7 +7943,7 @@
     </row>
     <row r="7" ht="16.2" customHeight="1">
       <c r="B7" s="10" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -7896,7 +7951,7 @@
     </row>
     <row r="8" ht="16.2" customHeight="1">
       <c r="B8" s="10" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
@@ -7904,7 +7959,7 @@
     </row>
     <row r="9" ht="16.2" customHeight="1">
       <c r="B9" s="10" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
@@ -7912,7 +7967,7 @@
     </row>
     <row r="10" ht="16.2" customHeight="1">
       <c r="B10" s="10" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -7920,7 +7975,7 @@
     </row>
     <row r="11" ht="16.2" customHeight="1">
       <c r="B11" s="10" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
@@ -7928,7 +7983,7 @@
     </row>
     <row r="12" ht="16.2" customHeight="1">
       <c r="B12" s="10" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -7936,7 +7991,7 @@
     </row>
     <row r="13" ht="16.2" customHeight="1">
       <c r="B13" s="10" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -7944,7 +7999,7 @@
     </row>
     <row r="14" ht="16.2" customHeight="1">
       <c r="B14" s="10" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
@@ -7952,7 +8007,7 @@
     </row>
     <row r="15" ht="16.2" customHeight="1">
       <c r="B15" s="10" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
@@ -7960,7 +8015,7 @@
     </row>
     <row r="16" ht="16.2" customHeight="1">
       <c r="B16" s="10" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -7968,7 +8023,7 @@
     </row>
     <row r="17" ht="16.2" customHeight="1">
       <c r="B17" s="10" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -7976,7 +8031,7 @@
     </row>
     <row r="18" ht="16.2" customHeight="1">
       <c r="B18" s="10" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -7984,7 +8039,7 @@
     </row>
     <row r="19" ht="16.2" customHeight="1">
       <c r="B19" s="10" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -7992,7 +8047,7 @@
     </row>
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="10" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -8000,7 +8055,7 @@
     </row>
     <row r="21" ht="16.2" customHeight="1">
       <c r="B21" s="10" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -8008,7 +8063,7 @@
     </row>
     <row r="22" ht="16.2" customHeight="1">
       <c r="B22" s="10" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
@@ -8016,7 +8071,7 @@
     </row>
     <row r="23" ht="16.2" customHeight="1">
       <c r="B23" s="10" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
@@ -8024,7 +8079,7 @@
     </row>
     <row r="24" ht="16.2" customHeight="1">
       <c r="B24" s="10" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
@@ -8032,7 +8087,7 @@
     </row>
     <row r="25" ht="16.2" customHeight="1">
       <c r="B25" s="10" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
@@ -8040,7 +8095,7 @@
     </row>
     <row r="26" ht="16.2" customHeight="1">
       <c r="B26" s="10" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
@@ -8048,7 +8103,7 @@
     </row>
     <row r="27" ht="16.2" customHeight="1">
       <c r="B27" s="10" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
@@ -8056,7 +8111,7 @@
     </row>
     <row r="28" ht="16.2" customHeight="1">
       <c r="B28" s="10" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
@@ -8064,7 +8119,7 @@
     </row>
     <row r="29" ht="16.2" customHeight="1">
       <c r="B29" s="10" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
@@ -8072,7 +8127,7 @@
     </row>
     <row r="30" ht="16.2" customHeight="1">
       <c r="B30" s="10" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
@@ -8080,7 +8135,7 @@
     </row>
     <row r="31" ht="16.2" customHeight="1">
       <c r="B31" s="10" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="10"/>
@@ -8088,7 +8143,7 @@
     </row>
     <row r="32" ht="16.2" customHeight="1">
       <c r="B32" s="10" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -8096,7 +8151,7 @@
     </row>
     <row r="33" ht="16.2" customHeight="1">
       <c r="B33" s="10" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -8104,7 +8159,7 @@
     </row>
     <row r="34" ht="16.2" customHeight="1">
       <c r="B34" s="10" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
@@ -8112,7 +8167,7 @@
     </row>
     <row r="35" ht="16.2" customHeight="1">
       <c r="B35" s="10" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
@@ -8120,7 +8175,7 @@
     </row>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="10" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
@@ -8128,7 +8183,7 @@
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
@@ -8136,7 +8191,7 @@
     </row>
     <row r="38" ht="16.2" customHeight="1">
       <c r="B38" s="10" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
@@ -8144,7 +8199,7 @@
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
@@ -8152,7 +8207,7 @@
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="11" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
@@ -8162,7 +8217,7 @@
     <row r="42" ht="8" customHeight="1"/>
     <row r="43" ht="24" customHeight="1">
       <c r="B43" s="4" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -8171,401 +8226,401 @@
     <row r="44" ht="4" customHeight="1"/>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="13" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
     </row>
     <row r="46" ht="32.4" customHeight="1">
       <c r="B46" s="14" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
     </row>
     <row r="47" ht="32.4" customHeight="1">
       <c r="B47" s="15" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="14" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
     </row>
     <row r="49" ht="32.4" customHeight="1">
       <c r="B49" s="15" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="14" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="15" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="14" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
     </row>
     <row r="53" ht="32.4" customHeight="1">
       <c r="B53" s="15" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="14" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="15" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="14" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="15" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
     </row>
     <row r="58" ht="32.4" customHeight="1">
       <c r="B58" s="14" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
     </row>
     <row r="59" ht="32.4" customHeight="1">
       <c r="B59" s="15" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
     </row>
     <row r="60" ht="32.4" customHeight="1">
       <c r="B60" s="14" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="15" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="B62" s="14" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="B63" s="15" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
     </row>
     <row r="64" ht="32.4" customHeight="1">
       <c r="B64" s="14" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
     </row>
     <row r="65" ht="32.4" customHeight="1">
       <c r="B65" s="15" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
     </row>
     <row r="66" ht="32.4" customHeight="1">
       <c r="B66" s="14" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="B67" s="15" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
     </row>
     <row r="68" ht="32.4" customHeight="1">
       <c r="B68" s="14" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
     </row>
     <row r="69" ht="32.4" customHeight="1">
       <c r="B69" s="15" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
     </row>
     <row r="70" ht="32.4" customHeight="1">
       <c r="B70" s="14" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
     </row>
     <row r="71" ht="32.4" customHeight="1">
       <c r="B71" s="15" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="B72" s="14" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
     </row>
     <row r="73" ht="6" customHeight="1"/>
     <row r="74" ht="8" customHeight="1"/>
     <row r="75" ht="24" customHeight="1">
       <c r="B75" s="4" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -8574,133 +8629,133 @@
     <row r="76" ht="4" customHeight="1"/>
     <row r="77" ht="18" customHeight="1">
       <c r="B77" s="13" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="E77" s="13"/>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="B78" s="14" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="E78" s="14"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="B79" s="15" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="E79" s="15"/>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="B80" s="14" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="E80" s="14"/>
     </row>
     <row r="81" ht="32.4" customHeight="1">
       <c r="B81" s="15" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="E81" s="15"/>
     </row>
     <row r="82" ht="32.4" customHeight="1">
       <c r="B82" s="14" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="E82" s="14"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="B83" s="15" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="E83" s="15"/>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="B84" s="14" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="E84" s="14"/>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="B85" s="15" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E85" s="15"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="B86" s="14" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="E86" s="14"/>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="B87" s="15" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="E87" s="15"/>
     </row>
@@ -8708,7 +8763,7 @@
     <row r="89" ht="8" customHeight="1"/>
     <row r="90" ht="24" customHeight="1">
       <c r="B90" s="4" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -8717,7 +8772,7 @@
     <row r="91" ht="4" customHeight="1"/>
     <row r="92" ht="18" customHeight="1">
       <c r="B92" s="7" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
@@ -8725,7 +8780,7 @@
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="B93" s="7" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
@@ -8733,7 +8788,7 @@
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="B94" s="7" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
@@ -8741,7 +8796,7 @@
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="B95" s="7" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
@@ -8839,7 +8894,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -8847,42 +8902,42 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8" ht="6" customHeight="1"/>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="24" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -8890,7 +8945,7 @@
     <row r="11" ht="4" customHeight="1"/>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="6" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -8905,42 +8960,42 @@
     </row>
     <row r="15" ht="16.2" customHeight="1">
       <c r="B15" s="10" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
     </row>
     <row r="16" ht="16.2" customHeight="1">
       <c r="B16" s="10" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
     </row>
     <row r="17" ht="16.2" customHeight="1">
       <c r="B17" s="10" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
     </row>
     <row r="18" ht="16.2" customHeight="1">
       <c r="B18" s="10" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
     </row>
     <row r="19" ht="16.2" customHeight="1">
       <c r="B19" s="10" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
     </row>
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="11" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -8955,21 +9010,21 @@
     </row>
     <row r="23" ht="16.2" customHeight="1">
       <c r="B23" s="10" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
     </row>
     <row r="24" ht="16.2" customHeight="1">
       <c r="B24" s="10" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
     </row>
     <row r="25" ht="16.2" customHeight="1">
       <c r="B25" s="11" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
@@ -8988,68 +9043,68 @@
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="14" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="14" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="15" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="14" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="15" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -9060,58 +9115,58 @@
         <v>169</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="15" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
     </row>
     <row r="36" ht="32.4" customHeight="1">
       <c r="B36" s="14" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="15" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
     </row>
     <row r="38" ht="32.4" customHeight="1">
       <c r="B38" s="14" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
     </row>
     <row r="39" ht="6" customHeight="1"/>
     <row r="40" ht="8" customHeight="1"/>
     <row r="41" ht="24" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -9119,7 +9174,7 @@
     <row r="42" ht="4" customHeight="1"/>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="13" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>194</v>
@@ -9130,152 +9185,152 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="14" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="15" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="14" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="15" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="14" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="15" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
     </row>
     <row r="50" ht="32.4" customHeight="1">
       <c r="B50" s="14" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="15" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="14" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="15" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="14" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="15" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="14" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
     </row>
     <row r="57" ht="6" customHeight="1"/>
     <row r="58" ht="8" customHeight="1"/>
     <row r="59" ht="24" customHeight="1">
       <c r="B59" s="4" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
@@ -9283,21 +9338,21 @@
     <row r="60" ht="4" customHeight="1"/>
     <row r="61" ht="16.2" customHeight="1">
       <c r="B61" s="9" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
     </row>
     <row r="62" ht="16.2" customHeight="1">
       <c r="B62" s="10" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
     </row>
     <row r="63" ht="16.2" customHeight="1">
       <c r="B63" s="11" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
@@ -9312,7 +9367,7 @@
     </row>
     <row r="66" ht="30.6" customHeight="1">
       <c r="B66" s="11" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
@@ -9320,14 +9375,14 @@
     <row r="67" ht="6" customHeight="1"/>
     <row r="68" ht="18" customHeight="1">
       <c r="B68" s="7" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="B69" s="7" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
@@ -9336,7 +9391,7 @@
     <row r="71" ht="8" customHeight="1"/>
     <row r="72" ht="24" customHeight="1">
       <c r="B72" s="4" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -9344,21 +9399,21 @@
     <row r="73" ht="4" customHeight="1"/>
     <row r="74" ht="18" customHeight="1">
       <c r="B74" s="7" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="B75" s="7" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="B76" s="7" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
@@ -9427,7 +9482,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -9435,7 +9490,7 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="6" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -9443,75 +9498,75 @@
     <row r="6" ht="6" customHeight="1"/>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="13" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
     </row>
     <row r="13" ht="6" customHeight="1"/>
     <row r="14" ht="8" customHeight="1"/>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -9519,49 +9574,49 @@
     <row r="16" ht="4" customHeight="1"/>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="7" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="7" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="7" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="7" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="7" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="7" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="7" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -9570,7 +9625,7 @@
     <row r="25" ht="8" customHeight="1"/>
     <row r="26" ht="24" customHeight="1">
       <c r="B26" s="4" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -9578,53 +9633,53 @@
     <row r="27" ht="4" customHeight="1"/>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="13" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="14" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="15" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
     </row>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="14" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
     </row>
     <row r="32" ht="6" customHeight="1"/>
     <row r="33" ht="8" customHeight="1"/>
     <row r="34" ht="24" customHeight="1">
       <c r="B34" s="4" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -9632,35 +9687,35 @@
     <row r="35" ht="4" customHeight="1"/>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="9" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="16.2" customHeight="1">
       <c r="B38" s="10" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="11" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
@@ -9669,7 +9724,7 @@
     <row r="42" ht="8" customHeight="1"/>
     <row r="43" ht="24" customHeight="1">
       <c r="B43" s="4" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -9677,21 +9732,21 @@
     <row r="44" ht="4" customHeight="1"/>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="7" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="7" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="7" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -9700,7 +9755,7 @@
     <row r="49" ht="8" customHeight="1"/>
     <row r="50" ht="24" customHeight="1">
       <c r="B50" s="4" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -9708,7 +9763,7 @@
     <row r="51" ht="4" customHeight="1"/>
     <row r="52" ht="46.8" customHeight="1">
       <c r="B52" s="6" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>

--- a/docs/JMeter_Usage_Guide.xlsx
+++ b/docs/JMeter_Usage_Guide.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="1059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="1062">
   <si>
     <t>JMeter APIテスト 利用方法</t>
   </si>
@@ -536,6 +536,15 @@
   </si>
   <si>
     <t>出力先フォルダ（既定: output）</t>
+  </si>
+  <si>
+    <t>-n ファイル名</t>
+  </si>
+  <si>
+    <t>-JmxName（-n）</t>
+  </si>
+  <si>
+    <t>出力する JMX のファイル名（例: order_test.jmx）。設定「出力JMXファイル名」（output_file）より優先します</t>
   </si>
   <si>
     <t>--split</t>
@@ -3068,10 +3077,10 @@
     <t>generate</t>
   </si>
   <si>
-    <t>./jmeter_api_tool.sh generate -i ファイル [-s 設定CSV] [-o フォルダ] [--split] [-f]</t>
-  </si>
-  <si>
-    <t>jmeter_api_tool.bat generate -i ファイル [-s 設定CSV] [-OutDir フォルダ] [-Split] [-Force]</t>
+    <t>./jmeter_api_tool.sh generate -i ファイル [-s 設定CSV] [-o フォルダ] [-n ファイル名] [--split] [-f]</t>
+  </si>
+  <si>
+    <t>jmeter_api_tool.bat generate -i ファイル [-s 設定CSV] [-OutDir フォルダ] [-JmxName ファイル名] [-Split] [-Force]</t>
   </si>
   <si>
     <t>JMX を生成（既定: output）</t>
@@ -3821,50 +3830,50 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C3" s="4"/>
     </row>
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="16.2" customHeight="1">
       <c r="B5" s="9" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C5" s="9"/>
     </row>
     <row r="6" ht="16.2" customHeight="1">
       <c r="B6" s="10" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" ht="16.2" customHeight="1">
       <c r="B7" s="10" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" ht="16.2" customHeight="1">
       <c r="B8" s="10" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" ht="16.2" customHeight="1">
       <c r="B9" s="10" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" ht="16.2" customHeight="1">
       <c r="B10" s="10" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C10" s="10"/>
     </row>
     <row r="11" ht="16.2" customHeight="1">
       <c r="B11" s="11" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -3872,55 +3881,55 @@
     <row r="13" ht="8" customHeight="1"/>
     <row r="14" ht="24" customHeight="1">
       <c r="B14" s="4" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15" ht="4" customHeight="1"/>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="13" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
     </row>
     <row r="17" ht="32.4" customHeight="1">
       <c r="B17" s="14" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="15" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="14" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
     </row>
     <row r="21" ht="6" customHeight="1"/>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="6" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="C22" s="6"/>
     </row>
@@ -3928,14 +3937,14 @@
     <row r="24" ht="8" customHeight="1"/>
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="4" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C25" s="4"/>
     </row>
     <row r="26" ht="4" customHeight="1"/>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="13" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>6</v>
@@ -3943,104 +3952,104 @@
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="14" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="14" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="15" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="14" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="15" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="14" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="15" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="14" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="15" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="14" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="39" ht="6" customHeight="1"/>
     <row r="40" ht="8" customHeight="1"/>
     <row r="41" ht="24" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="C41" s="4"/>
     </row>
     <row r="42" ht="4" customHeight="1"/>
     <row r="43" ht="46.8" customHeight="1">
       <c r="B43" s="6" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C43" s="6"/>
     </row>
@@ -4048,14 +4057,14 @@
     <row r="45" ht="8" customHeight="1"/>
     <row r="46" ht="24" customHeight="1">
       <c r="B46" s="4" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C46" s="4"/>
     </row>
     <row r="47" ht="4" customHeight="1"/>
     <row r="48" ht="32.4" customHeight="1">
       <c r="B48" s="6" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="C48" s="6"/>
     </row>
@@ -4063,26 +4072,26 @@
     <row r="50" ht="8" customHeight="1"/>
     <row r="51" ht="24" customHeight="1">
       <c r="B51" s="4" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C51" s="4"/>
     </row>
     <row r="52" ht="4" customHeight="1"/>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="7" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C53" s="7"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="7" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C54" s="7"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="7" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C55" s="7"/>
     </row>
@@ -4142,7 +4151,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -4150,10 +4159,10 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>6</v>
@@ -4161,97 +4170,97 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="15" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
     </row>
     <row r="14" ht="6" customHeight="1"/>
     <row r="15" ht="8" customHeight="1"/>
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="4" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -4259,152 +4268,152 @@
     <row r="17" ht="4" customHeight="1"/>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="13" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="14" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="14" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="15" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="14" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="15" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="14" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="15" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="14" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="15" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="14" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="15" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
     </row>
     <row r="31" ht="6" customHeight="1"/>
     <row r="32" ht="8" customHeight="1"/>
     <row r="33" ht="24" customHeight="1">
       <c r="B33" s="4" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -4412,21 +4421,21 @@
     <row r="34" ht="4" customHeight="1"/>
     <row r="35" ht="16.2" customHeight="1">
       <c r="B35" s="9" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
     </row>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="10" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
@@ -4440,21 +4449,21 @@
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="10" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="16.2" customHeight="1">
       <c r="B41" s="10" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
@@ -4468,28 +4477,28 @@
     </row>
     <row r="43" ht="16.2" customHeight="1">
       <c r="B43" s="10" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
     </row>
     <row r="44" ht="16.2" customHeight="1">
       <c r="B44" s="10" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
     </row>
     <row r="45" ht="16.2" customHeight="1">
       <c r="B45" s="10" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
     </row>
     <row r="46" ht="16.2" customHeight="1">
       <c r="B46" s="10" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C46" s="10"/>
       <c r="D46" s="10"/>
@@ -4503,14 +4512,14 @@
     </row>
     <row r="48" ht="16.2" customHeight="1">
       <c r="B48" s="10" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="10"/>
     </row>
     <row r="49" ht="16.2" customHeight="1">
       <c r="B49" s="11" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
@@ -4518,21 +4527,21 @@
     <row r="50" ht="6" customHeight="1"/>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="7" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="7" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="7" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -4541,7 +4550,7 @@
     <row r="55" ht="8" customHeight="1"/>
     <row r="56" ht="24" customHeight="1">
       <c r="B56" s="4" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
@@ -4549,60 +4558,60 @@
     <row r="57" ht="4" customHeight="1"/>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="13" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="D58" s="13"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="14" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="D59" s="14"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="15" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="D60" s="15"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="14" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="D61" s="14"/>
     </row>
     <row r="62" ht="32.4" customHeight="1">
       <c r="B62" s="15" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D62" s="15"/>
     </row>
     <row r="63" ht="6" customHeight="1"/>
     <row r="64" ht="18" customHeight="1">
       <c r="B64" s="7" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="B65" s="7" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -4611,7 +4620,7 @@
     <row r="67" ht="8" customHeight="1"/>
     <row r="68" ht="24" customHeight="1">
       <c r="B68" s="4" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
@@ -4619,55 +4628,55 @@
     <row r="69" ht="4" customHeight="1"/>
     <row r="70" ht="18" customHeight="1">
       <c r="B70" s="13" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="D70" s="13"/>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="B71" s="14" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="D71" s="14"/>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="B72" s="15" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="D72" s="15"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="B73" s="14" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D73" s="14"/>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="B74" s="15" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="D74" s="15"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="B75" s="14" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="D75" s="14"/>
     </row>
@@ -4744,200 +4753,200 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="13" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="B4" s="14" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="15" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
     </row>
     <row r="6" ht="32.4" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7" ht="32.4" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
     </row>
     <row r="8" ht="32.4" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
     </row>
     <row r="10" ht="32.4" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="11" ht="32.4" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
     </row>
     <row r="13" ht="32.4" customHeight="1">
       <c r="B13" s="15" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
     </row>
     <row r="14" ht="32.4" customHeight="1">
       <c r="B14" s="14" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="15" ht="32.4" customHeight="1">
       <c r="B15" s="15" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
     </row>
     <row r="16" ht="32.4" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="17" ht="32.4" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="19" ht="32.4" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="20" ht="32.4" customHeight="1">
       <c r="B20" s="14" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="21" ht="6" customHeight="1"/>
@@ -4979,7 +4988,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -4988,13 +4997,13 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>161</v>
@@ -5002,79 +5011,79 @@
     </row>
     <row r="6" ht="32.4" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="7" ht="32.4" customHeight="1">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="7" ht="46.8" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="8" ht="32.4" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>134</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="11" ht="6" customHeight="1"/>
     <row r="12" ht="8" customHeight="1"/>
     <row r="13" ht="24" customHeight="1">
       <c r="B13" s="4" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -5083,7 +5092,7 @@
     <row r="14" ht="4" customHeight="1"/>
     <row r="15" ht="18" customHeight="1">
       <c r="B15" s="13" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>161</v>
@@ -5093,50 +5102,50 @@
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="14" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
@@ -5146,107 +5155,107 @@
         <v>168</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="14" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="15" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="14" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="15" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="14" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="15" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="14" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="14" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="15" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="15"/>
@@ -6021,7 +6030,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -6235,7 +6244,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1">
+    <row r="40" ht="32.4" customHeight="1">
       <c r="B40" s="15" t="s">
         <v>171</v>
       </c>
@@ -6257,91 +6266,102 @@
         <v>176</v>
       </c>
     </row>
-    <row r="42" ht="6" customHeight="1"/>
-    <row r="43" ht="8" customHeight="1"/>
-    <row r="44" ht="24" customHeight="1">
-      <c r="B44" s="4" t="s">
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-    </row>
-    <row r="45" ht="4" customHeight="1"/>
-    <row r="46" ht="18" customHeight="1">
-      <c r="B46" s="13" t="s">
+      <c r="C42" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="D42" s="15" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1"/>
+    <row r="44" ht="8" customHeight="1"/>
+    <row r="45" ht="24" customHeight="1">
+      <c r="B45" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+    </row>
+    <row r="46" ht="4" customHeight="1"/>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C47" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="D46" s="13"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="B47" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="D47" s="14"/>
+      <c r="D47" s="13"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D48" s="14"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D48" s="15"/>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="B49" s="14" t="s">
+      <c r="C49" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="D49" s="15"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="D49" s="14"/>
-    </row>
-    <row r="50" ht="6" customHeight="1"/>
-    <row r="51" ht="8" customHeight="1"/>
-    <row r="52" ht="24" customHeight="1">
-      <c r="B52" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-    </row>
-    <row r="53" ht="4" customHeight="1"/>
-    <row r="54" ht="18" customHeight="1">
-      <c r="B54" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-    </row>
+      <c r="C50" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="D50" s="14"/>
+    </row>
+    <row r="51" ht="6" customHeight="1"/>
+    <row r="52" ht="8" customHeight="1"/>
+    <row r="53" ht="24" customHeight="1">
+      <c r="B53" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+    </row>
+    <row r="54" ht="4" customHeight="1"/>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" ht="6" customHeight="1"/>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+    </row>
+    <row r="59" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="B1:D1"/>
@@ -6365,16 +6385,16 @@
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="B45:D45"/>
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="C49:D49"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="B53:D53"/>
     <mergeCell ref="B55:D55"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B58:D58"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -6412,7 +6432,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -6422,7 +6442,7 @@
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -6431,7 +6451,7 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="7" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -6441,16 +6461,16 @@
     <row r="7" ht="6" customHeight="1"/>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="13" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>161</v>
@@ -6458,472 +6478,472 @@
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="14" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="15" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" ht="32.4" customHeight="1">
       <c r="B11" s="14" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="15" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="14" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>7</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="15" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>7</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" ht="32.4" customHeight="1">
       <c r="B15" s="14" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>7</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" ht="32.4" customHeight="1">
       <c r="B16" s="15" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" ht="32.4" customHeight="1">
       <c r="B17" s="14" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="15" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="14" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="14" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="15" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" ht="46.8" customHeight="1">
       <c r="B23" s="14" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" ht="61.2" customHeight="1">
       <c r="B24" s="15" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" ht="46.8" customHeight="1">
       <c r="B25" s="14" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="15" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="14" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D27" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="E27" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>262</v>
-      </c>
       <c r="F27" s="14" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="15" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="14" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="15" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="14" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="15" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="33" ht="32.4" customHeight="1">
       <c r="B33" s="14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="15" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="15" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>7</v>
@@ -6932,13 +6952,13 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>7</v>
@@ -6947,79 +6967,79 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="15" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="15" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F41" s="14"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="15" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>7</v>
@@ -7028,421 +7048,421 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F43" s="14"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="15" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="45" ht="32.4" customHeight="1">
       <c r="B45" s="14" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="15" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="14" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F47" s="14"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="15" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F48" s="15"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="14" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="15" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="51" ht="32.4" customHeight="1">
       <c r="B51" s="14" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="15" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="53" ht="32.4" customHeight="1">
       <c r="B53" s="14" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="15" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="56" ht="32.4" customHeight="1">
       <c r="B56" s="15" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="57" ht="32.4" customHeight="1">
       <c r="B57" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="58" ht="32.4" customHeight="1">
       <c r="B58" s="15" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="14" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="15" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="14" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="B62" s="15" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="B63" s="14" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="B64" s="15" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="B65" s="14" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="B66" s="15" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="B67" s="14" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="68" ht="6" customHeight="1"/>
@@ -7487,7 +7507,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -7496,16 +7516,16 @@
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>161</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" ht="32.4" customHeight="1">
@@ -7514,7 +7534,7 @@
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>7</v>
@@ -7522,198 +7542,198 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" ht="32.4" customHeight="1">
       <c r="B10" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>414</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>411</v>
-      </c>
       <c r="D10" s="14" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" ht="32.4" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="15" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="14" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15" ht="32.4" customHeight="1">
       <c r="B15" s="15" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" ht="32.4" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="14" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="14" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="15" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="14" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="15" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="22" ht="32.4" customHeight="1">
       <c r="B22" s="14" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -7722,7 +7742,7 @@
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E23" s="15"/>
     </row>
@@ -7730,7 +7750,7 @@
     <row r="25" ht="8" customHeight="1"/>
     <row r="26" ht="24" customHeight="1">
       <c r="B26" s="4" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -7739,7 +7759,7 @@
     <row r="27" ht="4" customHeight="1"/>
     <row r="28" ht="32.4" customHeight="1">
       <c r="B28" s="7" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -7747,7 +7767,7 @@
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="7" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -7755,7 +7775,7 @@
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="7" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -7763,7 +7783,7 @@
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="7" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -7771,7 +7791,7 @@
     </row>
     <row r="32" ht="32.4" customHeight="1">
       <c r="B32" s="7" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -7779,7 +7799,7 @@
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="7" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -7787,7 +7807,7 @@
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="7" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -7797,7 +7817,7 @@
     <row r="36" ht="8" customHeight="1"/>
     <row r="37" ht="24" customHeight="1">
       <c r="B37" s="4" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -7806,61 +7826,61 @@
     <row r="38" ht="4" customHeight="1"/>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="13" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E39" s="13"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="14" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E40" s="14"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="15" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E41" s="15"/>
     </row>
     <row r="42" ht="32.4" customHeight="1">
       <c r="B42" s="14" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E42" s="14"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="15" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E43" s="15"/>
     </row>
@@ -7918,7 +7938,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -7927,7 +7947,7 @@
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="16.2" customHeight="1">
       <c r="B5" s="9" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -7935,7 +7955,7 @@
     </row>
     <row r="6" ht="16.2" customHeight="1">
       <c r="B6" s="10" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -7943,7 +7963,7 @@
     </row>
     <row r="7" ht="16.2" customHeight="1">
       <c r="B7" s="10" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -7951,7 +7971,7 @@
     </row>
     <row r="8" ht="16.2" customHeight="1">
       <c r="B8" s="10" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
@@ -7959,7 +7979,7 @@
     </row>
     <row r="9" ht="16.2" customHeight="1">
       <c r="B9" s="10" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
@@ -7967,7 +7987,7 @@
     </row>
     <row r="10" ht="16.2" customHeight="1">
       <c r="B10" s="10" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -7975,7 +7995,7 @@
     </row>
     <row r="11" ht="16.2" customHeight="1">
       <c r="B11" s="10" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
@@ -7983,7 +8003,7 @@
     </row>
     <row r="12" ht="16.2" customHeight="1">
       <c r="B12" s="10" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -7991,7 +8011,7 @@
     </row>
     <row r="13" ht="16.2" customHeight="1">
       <c r="B13" s="10" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -7999,7 +8019,7 @@
     </row>
     <row r="14" ht="16.2" customHeight="1">
       <c r="B14" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
@@ -8007,7 +8027,7 @@
     </row>
     <row r="15" ht="16.2" customHeight="1">
       <c r="B15" s="10" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
@@ -8015,7 +8035,7 @@
     </row>
     <row r="16" ht="16.2" customHeight="1">
       <c r="B16" s="10" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -8023,7 +8043,7 @@
     </row>
     <row r="17" ht="16.2" customHeight="1">
       <c r="B17" s="10" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -8031,7 +8051,7 @@
     </row>
     <row r="18" ht="16.2" customHeight="1">
       <c r="B18" s="10" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -8039,7 +8059,7 @@
     </row>
     <row r="19" ht="16.2" customHeight="1">
       <c r="B19" s="10" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -8047,7 +8067,7 @@
     </row>
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="10" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -8055,7 +8075,7 @@
     </row>
     <row r="21" ht="16.2" customHeight="1">
       <c r="B21" s="10" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -8063,7 +8083,7 @@
     </row>
     <row r="22" ht="16.2" customHeight="1">
       <c r="B22" s="10" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
@@ -8071,7 +8091,7 @@
     </row>
     <row r="23" ht="16.2" customHeight="1">
       <c r="B23" s="10" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
@@ -8079,7 +8099,7 @@
     </row>
     <row r="24" ht="16.2" customHeight="1">
       <c r="B24" s="10" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
@@ -8087,7 +8107,7 @@
     </row>
     <row r="25" ht="16.2" customHeight="1">
       <c r="B25" s="10" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
@@ -8095,7 +8115,7 @@
     </row>
     <row r="26" ht="16.2" customHeight="1">
       <c r="B26" s="10" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
@@ -8103,7 +8123,7 @@
     </row>
     <row r="27" ht="16.2" customHeight="1">
       <c r="B27" s="10" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
@@ -8111,7 +8131,7 @@
     </row>
     <row r="28" ht="16.2" customHeight="1">
       <c r="B28" s="10" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
@@ -8119,7 +8139,7 @@
     </row>
     <row r="29" ht="16.2" customHeight="1">
       <c r="B29" s="10" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
@@ -8127,7 +8147,7 @@
     </row>
     <row r="30" ht="16.2" customHeight="1">
       <c r="B30" s="10" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
@@ -8135,7 +8155,7 @@
     </row>
     <row r="31" ht="16.2" customHeight="1">
       <c r="B31" s="10" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="10"/>
@@ -8143,7 +8163,7 @@
     </row>
     <row r="32" ht="16.2" customHeight="1">
       <c r="B32" s="10" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -8151,7 +8171,7 @@
     </row>
     <row r="33" ht="16.2" customHeight="1">
       <c r="B33" s="10" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -8159,7 +8179,7 @@
     </row>
     <row r="34" ht="16.2" customHeight="1">
       <c r="B34" s="10" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
@@ -8167,7 +8187,7 @@
     </row>
     <row r="35" ht="16.2" customHeight="1">
       <c r="B35" s="10" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
@@ -8175,7 +8195,7 @@
     </row>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="10" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
@@ -8183,7 +8203,7 @@
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
@@ -8191,7 +8211,7 @@
     </row>
     <row r="38" ht="16.2" customHeight="1">
       <c r="B38" s="10" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
@@ -8199,7 +8219,7 @@
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
@@ -8207,7 +8227,7 @@
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="11" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
@@ -8217,7 +8237,7 @@
     <row r="42" ht="8" customHeight="1"/>
     <row r="43" ht="24" customHeight="1">
       <c r="B43" s="4" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -8226,401 +8246,401 @@
     <row r="44" ht="4" customHeight="1"/>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="13" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="46" ht="32.4" customHeight="1">
       <c r="B46" s="14" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="47" ht="32.4" customHeight="1">
       <c r="B47" s="15" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="14" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="49" ht="32.4" customHeight="1">
       <c r="B49" s="15" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="14" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="15" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="14" t="s">
+        <v>545</v>
+      </c>
+      <c r="C52" s="14" t="s">
         <v>542</v>
       </c>
-      <c r="C52" s="14" t="s">
-        <v>539</v>
-      </c>
       <c r="D52" s="14" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="53" ht="32.4" customHeight="1">
       <c r="B53" s="15" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="14" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="15" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="14" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="15" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="58" ht="32.4" customHeight="1">
       <c r="B58" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="C58" s="14" t="s">
         <v>565</v>
       </c>
-      <c r="C58" s="14" t="s">
-        <v>562</v>
-      </c>
       <c r="D58" s="14" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="59" ht="32.4" customHeight="1">
       <c r="B59" s="15" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D59" s="15" t="s">
+        <v>573</v>
+      </c>
+      <c r="E59" s="15" t="s">
         <v>570</v>
-      </c>
-      <c r="E59" s="15" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="60" ht="32.4" customHeight="1">
       <c r="B60" s="14" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="15" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="B62" s="14" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="B63" s="15" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="64" ht="32.4" customHeight="1">
       <c r="B64" s="14" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="65" ht="32.4" customHeight="1">
       <c r="B65" s="15" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="66" ht="32.4" customHeight="1">
       <c r="B66" s="14" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="B67" s="15" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="68" ht="32.4" customHeight="1">
       <c r="B68" s="14" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="69" ht="32.4" customHeight="1">
       <c r="B69" s="15" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="70" ht="32.4" customHeight="1">
       <c r="B70" s="14" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="71" ht="32.4" customHeight="1">
       <c r="B71" s="15" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="B72" s="14" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="73" ht="6" customHeight="1"/>
     <row r="74" ht="8" customHeight="1"/>
     <row r="75" ht="24" customHeight="1">
       <c r="B75" s="4" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -8629,133 +8649,133 @@
     <row r="76" ht="4" customHeight="1"/>
     <row r="77" ht="18" customHeight="1">
       <c r="B77" s="13" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E77" s="13"/>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="B78" s="14" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="E78" s="14"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="B79" s="15" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="E79" s="15"/>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="B80" s="14" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E80" s="14"/>
     </row>
     <row r="81" ht="32.4" customHeight="1">
       <c r="B81" s="15" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E81" s="15"/>
     </row>
     <row r="82" ht="32.4" customHeight="1">
       <c r="B82" s="14" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E82" s="14"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="B83" s="15" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E83" s="15"/>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="B84" s="14" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="E84" s="14"/>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="B85" s="15" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E85" s="15"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="B86" s="14" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="E86" s="14"/>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="B87" s="15" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E87" s="15"/>
     </row>
@@ -8763,7 +8783,7 @@
     <row r="89" ht="8" customHeight="1"/>
     <row r="90" ht="24" customHeight="1">
       <c r="B90" s="4" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -8772,7 +8792,7 @@
     <row r="91" ht="4" customHeight="1"/>
     <row r="92" ht="18" customHeight="1">
       <c r="B92" s="7" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
@@ -8780,7 +8800,7 @@
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="B93" s="7" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
@@ -8788,7 +8808,7 @@
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="B94" s="7" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
@@ -8796,7 +8816,7 @@
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="B95" s="7" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
@@ -8894,7 +8914,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -8902,42 +8922,42 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8" ht="6" customHeight="1"/>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="24" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -8945,7 +8965,7 @@
     <row r="11" ht="4" customHeight="1"/>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="6" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -8960,42 +8980,42 @@
     </row>
     <row r="15" ht="16.2" customHeight="1">
       <c r="B15" s="10" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
     </row>
     <row r="16" ht="16.2" customHeight="1">
       <c r="B16" s="10" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
     </row>
     <row r="17" ht="16.2" customHeight="1">
       <c r="B17" s="10" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
     </row>
     <row r="18" ht="16.2" customHeight="1">
       <c r="B18" s="10" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
     </row>
     <row r="19" ht="16.2" customHeight="1">
       <c r="B19" s="10" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
     </row>
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="11" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -9010,21 +9030,21 @@
     </row>
     <row r="23" ht="16.2" customHeight="1">
       <c r="B23" s="10" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
     </row>
     <row r="24" ht="16.2" customHeight="1">
       <c r="B24" s="10" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
     </row>
     <row r="25" ht="16.2" customHeight="1">
       <c r="B25" s="11" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
@@ -9043,68 +9063,68 @@
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="14" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="14" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="15" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="14" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="15" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -9115,58 +9135,58 @@
         <v>169</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="15" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="36" ht="32.4" customHeight="1">
       <c r="B36" s="14" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="15" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
     </row>
     <row r="38" ht="32.4" customHeight="1">
       <c r="B38" s="14" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="39" ht="6" customHeight="1"/>
     <row r="40" ht="8" customHeight="1"/>
     <row r="41" ht="24" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -9174,10 +9194,10 @@
     <row r="42" ht="4" customHeight="1"/>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="13" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>161</v>
@@ -9185,152 +9205,152 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="14" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="15" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="14" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="15" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="14" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="15" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="50" ht="32.4" customHeight="1">
       <c r="B50" s="14" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="15" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="14" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="15" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="14" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="15" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="14" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
     </row>
     <row r="57" ht="6" customHeight="1"/>
     <row r="58" ht="8" customHeight="1"/>
     <row r="59" ht="24" customHeight="1">
       <c r="B59" s="4" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
@@ -9338,21 +9358,21 @@
     <row r="60" ht="4" customHeight="1"/>
     <row r="61" ht="16.2" customHeight="1">
       <c r="B61" s="9" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
     </row>
     <row r="62" ht="16.2" customHeight="1">
       <c r="B62" s="10" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
     </row>
     <row r="63" ht="16.2" customHeight="1">
       <c r="B63" s="11" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
@@ -9367,7 +9387,7 @@
     </row>
     <row r="66" ht="30.6" customHeight="1">
       <c r="B66" s="11" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
@@ -9375,14 +9395,14 @@
     <row r="67" ht="6" customHeight="1"/>
     <row r="68" ht="18" customHeight="1">
       <c r="B68" s="7" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="B69" s="7" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
@@ -9391,7 +9411,7 @@
     <row r="71" ht="8" customHeight="1"/>
     <row r="72" ht="24" customHeight="1">
       <c r="B72" s="4" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -9399,21 +9419,21 @@
     <row r="73" ht="4" customHeight="1"/>
     <row r="74" ht="18" customHeight="1">
       <c r="B74" s="7" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="B75" s="7" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="B76" s="7" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
@@ -9482,7 +9502,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -9490,7 +9510,7 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="6" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -9498,75 +9518,75 @@
     <row r="6" ht="6" customHeight="1"/>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="13" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
     </row>
     <row r="13" ht="6" customHeight="1"/>
     <row r="14" ht="8" customHeight="1"/>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -9574,49 +9594,49 @@
     <row r="16" ht="4" customHeight="1"/>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="7" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="7" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="7" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="7" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="7" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="7" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="7" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -9625,7 +9645,7 @@
     <row r="25" ht="8" customHeight="1"/>
     <row r="26" ht="24" customHeight="1">
       <c r="B26" s="4" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -9633,53 +9653,53 @@
     <row r="27" ht="4" customHeight="1"/>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="13" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="14" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="15" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
     </row>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="14" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
     </row>
     <row r="32" ht="6" customHeight="1"/>
     <row r="33" ht="8" customHeight="1"/>
     <row r="34" ht="24" customHeight="1">
       <c r="B34" s="4" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -9687,35 +9707,35 @@
     <row r="35" ht="4" customHeight="1"/>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="9" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="16.2" customHeight="1">
       <c r="B38" s="10" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="11" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
@@ -9724,7 +9744,7 @@
     <row r="42" ht="8" customHeight="1"/>
     <row r="43" ht="24" customHeight="1">
       <c r="B43" s="4" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -9732,21 +9752,21 @@
     <row r="44" ht="4" customHeight="1"/>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="7" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="7" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="7" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -9755,7 +9775,7 @@
     <row r="49" ht="8" customHeight="1"/>
     <row r="50" ht="24" customHeight="1">
       <c r="B50" s="4" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -9763,7 +9783,7 @@
     <row r="51" ht="4" customHeight="1"/>
     <row r="52" ht="46.8" customHeight="1">
       <c r="B52" s="6" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>

--- a/docs/JMeter_Usage_Guide.xlsx
+++ b/docs/JMeter_Usage_Guide.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="1062">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="1065">
   <si>
     <t>JMeter APIテスト 利用方法</t>
   </si>
@@ -214,6 +214,12 @@
     <t>入力テンプレート（CSV）：設定</t>
   </si>
   <si>
+    <t>input/openapi_config.csv</t>
+  </si>
+  <si>
+    <t>OpenAPI 定義（.json）から生成する場合の設定（接続先・HTTP ヘッダ・アクセストークン）。generate の -c / -OpenApiConfig で指定</t>
+  </si>
+  <si>
     <t>output/api_test.jmx</t>
   </si>
   <si>
@@ -454,7 +460,7 @@
     <t>.\jmeter_api_tool.bat init         # Windows 11</t>
   </si>
   <si>
-    <t>input フォルダに次の 3 ファイルが作成されます（既存ファイルは上書きしません。上書きする場合は -f / -Force を付けます）。</t>
+    <t>input フォルダに次の 4 ファイルが作成されます（既存ファイルは上書きしません。上書きする場合は -f / -Force を付けます）。</t>
   </si>
   <si>
     <t>・api_definition.xlsx（Excel 形式のテンプレート）</t>
@@ -466,6 +472,9 @@
     <t>・api_definition_settings.csv（CSV 形式：設定）</t>
   </si>
   <si>
+    <t>・openapi_config.csv（CSV 形式：OpenAPI 定義から生成する場合の接続先・HTTP ヘッダ・アクセストークン。generate の -c / -OpenApiConfig で指定）</t>
+  </si>
+  <si>
     <t>手順2：API 定義を記入する</t>
   </si>
   <si>
@@ -799,7 +808,7 @@
     <t>アクセストークンのフォルダ</t>
   </si>
   <si>
-    <t>指定すると、このフォルダ配下のファイルからアクセストークンを読み込み、共通ヘッダに Authorization: Bearer ${ACCESS_TOKEN} を付けます（共通ヘッダに Authorization がある場合はその値を使用）。空欄 = 使わない。JMX からの相対パスまたは絶対パス。-JACCESS_TOKEN_DIR</t>
+    <t>指定すると、このフォルダ配下のファイルからアクセストークンを読み込み、共通ヘッダに Authorization: Bearer ${ACCESS_TOKEN} を付けます（共通ヘッダに Authorization がある場合はその値を使用）。空欄 = 使わない。JMX からの相対パスまたは絶対パス（区切りは \ と / のどちらでも可。; で区切って複数書くと、存在する最初のフォルダを使用）。-JACCESS_TOKEN_DIR</t>
   </si>
   <si>
     <t>access_token_file</t>
@@ -811,7 +820,7 @@
     <t>access_token.txt</t>
   </si>
   <si>
-    <t>アクセストークンを書いたファイルの名前（フォルダからの相対パス）。前後の空白・改行は除き、実行中にファイルが更新されると読み直します。-JACCESS_TOKEN_FILE</t>
+    <t>アクセストークンを書いたファイルの名前（フォルダからの相対パス）。*.token のように * を含めると、一致するファイルのうち更新日時が最も新しいファイルを使います。前後の空白・改行は除き、実行中にファイルが更新されると読み直します。-JACCESS_TOKEN_FILE</t>
   </si>
   <si>
     <t>follow_redirects</t>
@@ -3830,50 +3839,50 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C3" s="4"/>
     </row>
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="16.2" customHeight="1">
       <c r="B5" s="9" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="C5" s="9"/>
     </row>
     <row r="6" ht="16.2" customHeight="1">
       <c r="B6" s="10" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" ht="16.2" customHeight="1">
       <c r="B7" s="10" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" ht="16.2" customHeight="1">
       <c r="B8" s="10" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" ht="16.2" customHeight="1">
       <c r="B9" s="10" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" ht="16.2" customHeight="1">
       <c r="B10" s="10" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C10" s="10"/>
     </row>
     <row r="11" ht="16.2" customHeight="1">
       <c r="B11" s="11" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -3881,55 +3890,55 @@
     <row r="13" ht="8" customHeight="1"/>
     <row r="14" ht="24" customHeight="1">
       <c r="B14" s="4" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15" ht="4" customHeight="1"/>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="13" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
     </row>
     <row r="17" ht="32.4" customHeight="1">
       <c r="B17" s="14" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="15" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="14" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
     </row>
     <row r="21" ht="6" customHeight="1"/>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="6" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C22" s="6"/>
     </row>
@@ -3937,14 +3946,14 @@
     <row r="24" ht="8" customHeight="1"/>
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="4" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C25" s="4"/>
     </row>
     <row r="26" ht="4" customHeight="1"/>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="13" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>6</v>
@@ -3952,104 +3961,104 @@
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="14" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="14" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="15" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="14" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="15" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="14" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="15" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="14" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="15" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="14" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
     </row>
     <row r="39" ht="6" customHeight="1"/>
     <row r="40" ht="8" customHeight="1"/>
     <row r="41" ht="24" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="C41" s="4"/>
     </row>
     <row r="42" ht="4" customHeight="1"/>
     <row r="43" ht="46.8" customHeight="1">
       <c r="B43" s="6" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C43" s="6"/>
     </row>
@@ -4057,14 +4066,14 @@
     <row r="45" ht="8" customHeight="1"/>
     <row r="46" ht="24" customHeight="1">
       <c r="B46" s="4" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C46" s="4"/>
     </row>
     <row r="47" ht="4" customHeight="1"/>
     <row r="48" ht="32.4" customHeight="1">
       <c r="B48" s="6" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C48" s="6"/>
     </row>
@@ -4072,26 +4081,26 @@
     <row r="50" ht="8" customHeight="1"/>
     <row r="51" ht="24" customHeight="1">
       <c r="B51" s="4" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C51" s="4"/>
     </row>
     <row r="52" ht="4" customHeight="1"/>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="7" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="C53" s="7"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="7" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C54" s="7"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="7" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C55" s="7"/>
     </row>
@@ -4151,7 +4160,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -4159,10 +4168,10 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>6</v>
@@ -4170,97 +4179,97 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="15" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
     </row>
     <row r="14" ht="6" customHeight="1"/>
     <row r="15" ht="8" customHeight="1"/>
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="4" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -4268,152 +4277,152 @@
     <row r="17" ht="4" customHeight="1"/>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="13" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="14" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="14" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="15" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="14" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="15" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="14" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="15" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="14" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="15" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="14" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="15" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
     </row>
     <row r="31" ht="6" customHeight="1"/>
     <row r="32" ht="8" customHeight="1"/>
     <row r="33" ht="24" customHeight="1">
       <c r="B33" s="4" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -4421,105 +4430,105 @@
     <row r="34" ht="4" customHeight="1"/>
     <row r="35" ht="16.2" customHeight="1">
       <c r="B35" s="9" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
     </row>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="10" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="16.2" customHeight="1">
       <c r="B38" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="10" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="16.2" customHeight="1">
       <c r="B41" s="10" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
     </row>
     <row r="42" ht="16.2" customHeight="1">
       <c r="B42" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C42" s="10"/>
       <c r="D42" s="10"/>
     </row>
     <row r="43" ht="16.2" customHeight="1">
       <c r="B43" s="10" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
     </row>
     <row r="44" ht="16.2" customHeight="1">
       <c r="B44" s="10" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
     </row>
     <row r="45" ht="16.2" customHeight="1">
       <c r="B45" s="10" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
     </row>
     <row r="46" ht="16.2" customHeight="1">
       <c r="B46" s="10" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C46" s="10"/>
       <c r="D46" s="10"/>
     </row>
     <row r="47" ht="16.2" customHeight="1">
       <c r="B47" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="10"/>
     </row>
     <row r="48" ht="16.2" customHeight="1">
       <c r="B48" s="10" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="10"/>
     </row>
     <row r="49" ht="16.2" customHeight="1">
       <c r="B49" s="11" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
@@ -4527,21 +4536,21 @@
     <row r="50" ht="6" customHeight="1"/>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="7" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="7" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="7" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -4550,7 +4559,7 @@
     <row r="55" ht="8" customHeight="1"/>
     <row r="56" ht="24" customHeight="1">
       <c r="B56" s="4" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
@@ -4558,60 +4567,60 @@
     <row r="57" ht="4" customHeight="1"/>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="13" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="D58" s="13"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="14" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="D59" s="14"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="15" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="D60" s="15"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="14" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="D61" s="14"/>
     </row>
     <row r="62" ht="32.4" customHeight="1">
       <c r="B62" s="15" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="D62" s="15"/>
     </row>
     <row r="63" ht="6" customHeight="1"/>
     <row r="64" ht="18" customHeight="1">
       <c r="B64" s="7" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="B65" s="7" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -4620,7 +4629,7 @@
     <row r="67" ht="8" customHeight="1"/>
     <row r="68" ht="24" customHeight="1">
       <c r="B68" s="4" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
@@ -4628,55 +4637,55 @@
     <row r="69" ht="4" customHeight="1"/>
     <row r="70" ht="18" customHeight="1">
       <c r="B70" s="13" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D70" s="13"/>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="B71" s="14" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="D71" s="14"/>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="B72" s="15" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D72" s="15"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="B73" s="14" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D73" s="14"/>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="B74" s="15" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="D74" s="15"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="B75" s="14" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="D75" s="14"/>
     </row>
@@ -4753,200 +4762,200 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="13" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="B4" s="14" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="15" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="6" ht="32.4" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
     </row>
     <row r="7" ht="32.4" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
     </row>
     <row r="8" ht="32.4" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="10" ht="32.4" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="11" ht="32.4" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
     </row>
     <row r="13" ht="32.4" customHeight="1">
       <c r="B13" s="15" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="14" ht="32.4" customHeight="1">
       <c r="B14" s="14" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
     </row>
     <row r="15" ht="32.4" customHeight="1">
       <c r="B15" s="15" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="16" ht="32.4" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
     </row>
     <row r="17" ht="32.4" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="19" ht="32.4" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="20" ht="32.4" customHeight="1">
       <c r="B20" s="14" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="21" ht="6" customHeight="1"/>
@@ -4988,7 +4997,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -4997,93 +5006,93 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" ht="32.4" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="7" ht="46.8" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="8" ht="32.4" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="11" ht="6" customHeight="1"/>
     <row r="12" ht="8" customHeight="1"/>
     <row r="13" ht="24" customHeight="1">
       <c r="B13" s="4" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -5092,170 +5101,170 @@
     <row r="14" ht="4" customHeight="1"/>
     <row r="15" ht="18" customHeight="1">
       <c r="B15" s="13" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="14" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="14" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="15" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="14" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="15" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="14" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="15" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="14" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="14" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="15" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="15"/>
@@ -5297,7 +5306,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -5414,7 +5423,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
+    <row r="21" ht="32.4" customHeight="1">
       <c r="B21" s="14" t="s">
         <v>63</v>
       </c>
@@ -5454,59 +5463,67 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" ht="6" customHeight="1"/>
-    <row r="27" ht="8" customHeight="1"/>
-    <row r="28" ht="24" customHeight="1">
-      <c r="B28" s="4" t="s">
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="4"/>
-    </row>
-    <row r="29" ht="4" customHeight="1"/>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="7" t="s">
+      <c r="C26" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C30" s="7"/>
-    </row>
+    </row>
+    <row r="27" ht="6" customHeight="1"/>
+    <row r="28" ht="8" customHeight="1"/>
+    <row r="29" ht="24" customHeight="1">
+      <c r="B29" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" ht="4" customHeight="1"/>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C31" s="7"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C32" s="7"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" s="7"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C34" s="7"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" s="7"/>
     </row>
-    <row r="36" ht="6" customHeight="1"/>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C37" s="8"/>
-    </row>
-    <row r="38" ht="6" customHeight="1"/>
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="7"/>
+    </row>
+    <row r="37" ht="6" customHeight="1"/>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="8"/>
+    </row>
+    <row r="39" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="B1:C1"/>
@@ -5517,14 +5534,14 @@
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -5560,7 +5577,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -5569,79 +5586,79 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" ht="32.4" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" ht="32.4" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" ht="32.4" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="8" customHeight="1"/>
     <row r="12" ht="24" customHeight="1">
       <c r="B12" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -5650,7 +5667,7 @@
     <row r="13" ht="4" customHeight="1"/>
     <row r="14" ht="16.2" customHeight="1">
       <c r="B14" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -5658,7 +5675,7 @@
     </row>
     <row r="15" ht="16.2" customHeight="1">
       <c r="B15" s="10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
@@ -5666,7 +5683,7 @@
     </row>
     <row r="16" ht="16.2" customHeight="1">
       <c r="B16" s="10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -5674,7 +5691,7 @@
     </row>
     <row r="17" ht="16.2" customHeight="1">
       <c r="B17" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -5682,7 +5699,7 @@
     </row>
     <row r="18" ht="16.2" customHeight="1">
       <c r="B18" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -5690,7 +5707,7 @@
     </row>
     <row r="19" ht="16.2" customHeight="1">
       <c r="B19" s="10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -5698,7 +5715,7 @@
     </row>
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -5706,7 +5723,7 @@
     </row>
     <row r="21" ht="16.2" customHeight="1">
       <c r="B21" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -5714,7 +5731,7 @@
     </row>
     <row r="22" ht="16.2" customHeight="1">
       <c r="B22" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
@@ -5722,7 +5739,7 @@
     </row>
     <row r="23" ht="16.2" customHeight="1">
       <c r="B23" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
@@ -5730,7 +5747,7 @@
     </row>
     <row r="24" ht="16.2" customHeight="1">
       <c r="B24" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
@@ -5738,7 +5755,7 @@
     </row>
     <row r="25" ht="16.2" customHeight="1">
       <c r="B25" s="10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
@@ -5746,7 +5763,7 @@
     </row>
     <row r="26" ht="16.2" customHeight="1">
       <c r="B26" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
@@ -5754,7 +5771,7 @@
     </row>
     <row r="27" ht="16.2" customHeight="1">
       <c r="B27" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
@@ -5762,7 +5779,7 @@
     </row>
     <row r="28" ht="16.2" customHeight="1">
       <c r="B28" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
@@ -5770,7 +5787,7 @@
     </row>
     <row r="29" ht="16.2" customHeight="1">
       <c r="B29" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
@@ -5779,7 +5796,7 @@
     <row r="30" ht="6" customHeight="1"/>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -5787,7 +5804,7 @@
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -5795,7 +5812,7 @@
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -5805,7 +5822,7 @@
     <row r="35" ht="8" customHeight="1"/>
     <row r="36" ht="24" customHeight="1">
       <c r="B36" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -5814,7 +5831,7 @@
     <row r="37" ht="4" customHeight="1"/>
     <row r="38" ht="32.4" customHeight="1">
       <c r="B38" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -5822,7 +5839,7 @@
     </row>
     <row r="39" ht="32.4" customHeight="1">
       <c r="B39" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -5830,7 +5847,7 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
@@ -5838,7 +5855,7 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -5847,7 +5864,7 @@
     <row r="42" ht="6" customHeight="1"/>
     <row r="43" ht="16.2" customHeight="1">
       <c r="B43" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
@@ -5855,7 +5872,7 @@
     </row>
     <row r="44" ht="16.2" customHeight="1">
       <c r="B44" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
@@ -5863,7 +5880,7 @@
     </row>
     <row r="45" ht="16.2" customHeight="1">
       <c r="B45" s="10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
@@ -5871,7 +5888,7 @@
     </row>
     <row r="46" ht="16.2" customHeight="1">
       <c r="B46" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
@@ -5881,7 +5898,7 @@
     <row r="48" ht="8" customHeight="1"/>
     <row r="49" ht="24" customHeight="1">
       <c r="B49" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
@@ -5890,7 +5907,7 @@
     <row r="50" ht="4" customHeight="1"/>
     <row r="51" ht="32.4" customHeight="1">
       <c r="B51" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -5899,7 +5916,7 @@
     <row r="52" ht="6" customHeight="1"/>
     <row r="53" ht="16.2" customHeight="1">
       <c r="B53" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
@@ -5907,7 +5924,7 @@
     </row>
     <row r="54" ht="16.2" customHeight="1">
       <c r="B54" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
@@ -5915,7 +5932,7 @@
     </row>
     <row r="55" ht="16.2" customHeight="1">
       <c r="B55" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
@@ -5923,7 +5940,7 @@
     </row>
     <row r="56" ht="16.2" customHeight="1">
       <c r="B56" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
@@ -5932,7 +5949,7 @@
     <row r="57" ht="6" customHeight="1"/>
     <row r="58" ht="16.2" customHeight="1">
       <c r="B58" s="9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
@@ -5940,7 +5957,7 @@
     </row>
     <row r="59" ht="16.2" customHeight="1">
       <c r="B59" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
@@ -5948,7 +5965,7 @@
     </row>
     <row r="60" ht="16.2" customHeight="1">
       <c r="B60" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
@@ -5957,7 +5974,7 @@
     <row r="61" ht="6" customHeight="1"/>
     <row r="62" ht="32.4" customHeight="1">
       <c r="B62" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
@@ -5965,7 +5982,7 @@
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="B63" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -6030,7 +6047,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -6049,7 +6066,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -6057,7 +6074,7 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="16.2" customHeight="1">
       <c r="B5" s="12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -6065,7 +6082,7 @@
     <row r="6" ht="6" customHeight="1"/>
     <row r="7" ht="16.2" customHeight="1">
       <c r="B7" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
@@ -6073,7 +6090,7 @@
     <row r="8" ht="6" customHeight="1"/>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -6081,289 +6098,296 @@
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
     </row>
-    <row r="14" ht="6" customHeight="1"/>
-    <row r="15" ht="8" customHeight="1"/>
-    <row r="16" ht="24" customHeight="1">
-      <c r="B16" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" ht="4" customHeight="1"/>
-    <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+    </row>
+    <row r="15" ht="6" customHeight="1"/>
+    <row r="16" ht="8" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1">
+      <c r="B17" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" ht="4" customHeight="1"/>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
     </row>
-    <row r="20" ht="32.4" customHeight="1">
+    <row r="20" ht="18" customHeight="1">
       <c r="B20" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
-    <row r="21" ht="18" customHeight="1">
+    <row r="21" ht="32.4" customHeight="1">
       <c r="B21" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
     </row>
-    <row r="22" ht="6" customHeight="1"/>
-    <row r="23" ht="32.4" customHeight="1">
-      <c r="B23" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-    </row>
-    <row r="24" ht="6" customHeight="1"/>
-    <row r="25" ht="8" customHeight="1"/>
-    <row r="26" ht="24" customHeight="1">
-      <c r="B26" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" ht="4" customHeight="1"/>
-    <row r="28" ht="16.2" customHeight="1">
-      <c r="B28" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" ht="6" customHeight="1"/>
+    <row r="24" ht="32.4" customHeight="1">
+      <c r="B24" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" ht="6" customHeight="1"/>
+    <row r="26" ht="8" customHeight="1"/>
+    <row r="27" ht="24" customHeight="1">
+      <c r="B27" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" ht="4" customHeight="1"/>
     <row r="29" ht="16.2" customHeight="1">
-      <c r="B29" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
+      <c r="B29" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
     </row>
     <row r="30" ht="16.2" customHeight="1">
-      <c r="B30" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-    </row>
-    <row r="31" ht="6" customHeight="1"/>
-    <row r="32" ht="16.2" customHeight="1">
-      <c r="B32" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-    </row>
+      <c r="B30" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+    </row>
+    <row r="31" ht="16.2" customHeight="1">
+      <c r="B31" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+    </row>
+    <row r="32" ht="6" customHeight="1"/>
     <row r="33" ht="16.2" customHeight="1">
-      <c r="B33" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
+      <c r="B33" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
     </row>
     <row r="34" ht="16.2" customHeight="1">
-      <c r="B34" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-    </row>
-    <row r="35" ht="6" customHeight="1"/>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="C36" s="13" t="s">
+      <c r="B34" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+    </row>
+    <row r="35" ht="16.2" customHeight="1">
+      <c r="B35" s="11" t="s">
         <v>161</v>
       </c>
-    </row>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+    </row>
+    <row r="36" ht="6" customHeight="1"/>
     <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="13" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="38" ht="32.4" customHeight="1">
-      <c r="B38" s="15" t="s">
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="14" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="B39" s="14" t="s">
+    <row r="39" ht="32.4" customHeight="1">
+      <c r="B39" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="15" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="40" ht="32.4" customHeight="1">
-      <c r="B40" s="15" t="s">
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="14" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="B41" s="14" t="s">
+    <row r="41" ht="32.4" customHeight="1">
+      <c r="B41" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="15" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="14" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="43" ht="6" customHeight="1"/>
-    <row r="44" ht="8" customHeight="1"/>
-    <row r="45" ht="24" customHeight="1">
-      <c r="B45" s="4" t="s">
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-    </row>
-    <row r="46" ht="4" customHeight="1"/>
-    <row r="47" ht="18" customHeight="1">
-      <c r="B47" s="13" t="s">
+      <c r="C43" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C47" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D47" s="13"/>
-    </row>
+      <c r="D43" s="15" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44" ht="6" customHeight="1"/>
+    <row r="45" ht="8" customHeight="1"/>
+    <row r="46" ht="24" customHeight="1">
+      <c r="B46" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+    </row>
+    <row r="47" ht="4" customHeight="1"/>
     <row r="48" ht="18" customHeight="1">
-      <c r="B48" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="D48" s="14"/>
+      <c r="B48" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D48" s="13"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="B49" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C49" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="D49" s="15"/>
+      <c r="B49" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="D49" s="14"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C50" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D50" s="14"/>
-    </row>
-    <row r="51" ht="6" customHeight="1"/>
-    <row r="52" ht="8" customHeight="1"/>
-    <row r="53" ht="24" customHeight="1">
-      <c r="B53" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-    </row>
-    <row r="54" ht="4" customHeight="1"/>
-    <row r="55" ht="18" customHeight="1">
-      <c r="B55" s="7" t="s">
+      <c r="C50" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-    </row>
+      <c r="D50" s="15"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="D51" s="14"/>
+    </row>
+    <row r="52" ht="6" customHeight="1"/>
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="24" customHeight="1">
+      <c r="B54" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+    </row>
+    <row r="55" ht="4" customHeight="1"/>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="7" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
     </row>
-    <row r="59" ht="6" customHeight="1"/>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+    </row>
+    <row r="60" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
@@ -6372,29 +6396,30 @@
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B46:D46"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="C49:D49"/>
     <mergeCell ref="C50:D50"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="B54:D54"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -6432,7 +6457,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -6442,7 +6467,7 @@
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -6451,7 +6476,7 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="7" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -6461,489 +6486,489 @@
     <row r="7" ht="6" customHeight="1"/>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="13" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="14" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="15" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" ht="32.4" customHeight="1">
       <c r="B11" s="14" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="15" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="14" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>7</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>7</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" ht="32.4" customHeight="1">
       <c r="B15" s="14" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>7</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" ht="32.4" customHeight="1">
       <c r="B16" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" ht="32.4" customHeight="1">
       <c r="B17" s="14" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="14" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" ht="46.8" customHeight="1">
       <c r="B23" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="24" ht="61.2" customHeight="1">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="24" ht="75.6" customHeight="1">
       <c r="B24" s="15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="25" ht="46.8" customHeight="1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="25" ht="61.2" customHeight="1">
       <c r="B25" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D27" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="E27" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>265</v>
-      </c>
       <c r="F27" s="14" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="14" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="15" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="14" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="15" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" ht="32.4" customHeight="1">
       <c r="B33" s="14" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="15" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="14" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="15" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>7</v>
@@ -6952,13 +6977,13 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="14" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>7</v>
@@ -6967,79 +6992,79 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="15" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="14" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="15" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="14" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F41" s="14"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="15" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>7</v>
@@ -7048,421 +7073,421 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="14" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F43" s="14"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="15" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="45" ht="32.4" customHeight="1">
       <c r="B45" s="14" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="15" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="14" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F47" s="14"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="15" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F48" s="15"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="14" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="15" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="51" ht="32.4" customHeight="1">
       <c r="B51" s="14" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="15" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="53" ht="32.4" customHeight="1">
       <c r="B53" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="15" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="14" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="56" ht="32.4" customHeight="1">
       <c r="B56" s="15" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="57" ht="32.4" customHeight="1">
       <c r="B57" s="14" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="58" ht="32.4" customHeight="1">
       <c r="B58" s="15" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="14" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="15" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="14" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="B62" s="15" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="B63" s="14" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="B64" s="15" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="B65" s="14" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="B66" s="15" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="B67" s="14" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="68" ht="6" customHeight="1"/>
@@ -7507,7 +7532,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -7516,16 +7541,16 @@
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" ht="32.4" customHeight="1">
@@ -7534,7 +7559,7 @@
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>7</v>
@@ -7542,207 +7567,207 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" ht="32.4" customHeight="1">
       <c r="B10" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>417</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>414</v>
-      </c>
       <c r="D10" s="14" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11" ht="32.4" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="15" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="14" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" ht="32.4" customHeight="1">
       <c r="B15" s="15" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" ht="32.4" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="14" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="14" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="15" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="14" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="15" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="22" ht="32.4" customHeight="1">
       <c r="B22" s="14" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E23" s="15"/>
     </row>
@@ -7750,7 +7775,7 @@
     <row r="25" ht="8" customHeight="1"/>
     <row r="26" ht="24" customHeight="1">
       <c r="B26" s="4" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -7759,7 +7784,7 @@
     <row r="27" ht="4" customHeight="1"/>
     <row r="28" ht="32.4" customHeight="1">
       <c r="B28" s="7" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -7767,7 +7792,7 @@
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="7" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -7775,7 +7800,7 @@
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="7" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -7783,7 +7808,7 @@
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="7" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -7791,7 +7816,7 @@
     </row>
     <row r="32" ht="32.4" customHeight="1">
       <c r="B32" s="7" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -7799,7 +7824,7 @@
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="7" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -7807,7 +7832,7 @@
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="7" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -7817,7 +7842,7 @@
     <row r="36" ht="8" customHeight="1"/>
     <row r="37" ht="24" customHeight="1">
       <c r="B37" s="4" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -7826,61 +7851,61 @@
     <row r="38" ht="4" customHeight="1"/>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="13" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E39" s="13"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="14" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E40" s="14"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="15" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E41" s="15"/>
     </row>
     <row r="42" ht="32.4" customHeight="1">
       <c r="B42" s="14" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E42" s="14"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="15" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E43" s="15"/>
     </row>
@@ -7938,7 +7963,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -7947,7 +7972,7 @@
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="16.2" customHeight="1">
       <c r="B5" s="9" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -7955,7 +7980,7 @@
     </row>
     <row r="6" ht="16.2" customHeight="1">
       <c r="B6" s="10" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -7963,7 +7988,7 @@
     </row>
     <row r="7" ht="16.2" customHeight="1">
       <c r="B7" s="10" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -7971,7 +7996,7 @@
     </row>
     <row r="8" ht="16.2" customHeight="1">
       <c r="B8" s="10" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
@@ -7979,7 +8004,7 @@
     </row>
     <row r="9" ht="16.2" customHeight="1">
       <c r="B9" s="10" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
@@ -7987,7 +8012,7 @@
     </row>
     <row r="10" ht="16.2" customHeight="1">
       <c r="B10" s="10" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -7995,7 +8020,7 @@
     </row>
     <row r="11" ht="16.2" customHeight="1">
       <c r="B11" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
@@ -8003,7 +8028,7 @@
     </row>
     <row r="12" ht="16.2" customHeight="1">
       <c r="B12" s="10" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -8011,7 +8036,7 @@
     </row>
     <row r="13" ht="16.2" customHeight="1">
       <c r="B13" s="10" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -8019,7 +8044,7 @@
     </row>
     <row r="14" ht="16.2" customHeight="1">
       <c r="B14" s="10" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
@@ -8027,7 +8052,7 @@
     </row>
     <row r="15" ht="16.2" customHeight="1">
       <c r="B15" s="10" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
@@ -8035,7 +8060,7 @@
     </row>
     <row r="16" ht="16.2" customHeight="1">
       <c r="B16" s="10" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -8043,7 +8068,7 @@
     </row>
     <row r="17" ht="16.2" customHeight="1">
       <c r="B17" s="10" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -8051,7 +8076,7 @@
     </row>
     <row r="18" ht="16.2" customHeight="1">
       <c r="B18" s="10" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -8059,7 +8084,7 @@
     </row>
     <row r="19" ht="16.2" customHeight="1">
       <c r="B19" s="10" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -8067,7 +8092,7 @@
     </row>
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="10" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -8075,7 +8100,7 @@
     </row>
     <row r="21" ht="16.2" customHeight="1">
       <c r="B21" s="10" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -8083,7 +8108,7 @@
     </row>
     <row r="22" ht="16.2" customHeight="1">
       <c r="B22" s="10" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
@@ -8091,7 +8116,7 @@
     </row>
     <row r="23" ht="16.2" customHeight="1">
       <c r="B23" s="10" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
@@ -8099,7 +8124,7 @@
     </row>
     <row r="24" ht="16.2" customHeight="1">
       <c r="B24" s="10" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
@@ -8107,7 +8132,7 @@
     </row>
     <row r="25" ht="16.2" customHeight="1">
       <c r="B25" s="10" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
@@ -8115,7 +8140,7 @@
     </row>
     <row r="26" ht="16.2" customHeight="1">
       <c r="B26" s="10" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
@@ -8123,7 +8148,7 @@
     </row>
     <row r="27" ht="16.2" customHeight="1">
       <c r="B27" s="10" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
@@ -8131,7 +8156,7 @@
     </row>
     <row r="28" ht="16.2" customHeight="1">
       <c r="B28" s="10" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
@@ -8139,7 +8164,7 @@
     </row>
     <row r="29" ht="16.2" customHeight="1">
       <c r="B29" s="10" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
@@ -8147,7 +8172,7 @@
     </row>
     <row r="30" ht="16.2" customHeight="1">
       <c r="B30" s="10" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
@@ -8155,7 +8180,7 @@
     </row>
     <row r="31" ht="16.2" customHeight="1">
       <c r="B31" s="10" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="10"/>
@@ -8163,7 +8188,7 @@
     </row>
     <row r="32" ht="16.2" customHeight="1">
       <c r="B32" s="10" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -8171,7 +8196,7 @@
     </row>
     <row r="33" ht="16.2" customHeight="1">
       <c r="B33" s="10" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -8179,7 +8204,7 @@
     </row>
     <row r="34" ht="16.2" customHeight="1">
       <c r="B34" s="10" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
@@ -8187,7 +8212,7 @@
     </row>
     <row r="35" ht="16.2" customHeight="1">
       <c r="B35" s="10" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
@@ -8195,7 +8220,7 @@
     </row>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="10" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
@@ -8203,7 +8228,7 @@
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
@@ -8211,7 +8236,7 @@
     </row>
     <row r="38" ht="16.2" customHeight="1">
       <c r="B38" s="10" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
@@ -8219,7 +8244,7 @@
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
@@ -8227,7 +8252,7 @@
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="11" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
@@ -8237,7 +8262,7 @@
     <row r="42" ht="8" customHeight="1"/>
     <row r="43" ht="24" customHeight="1">
       <c r="B43" s="4" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -8246,401 +8271,401 @@
     <row r="44" ht="4" customHeight="1"/>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="13" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="46" ht="32.4" customHeight="1">
       <c r="B46" s="14" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="47" ht="32.4" customHeight="1">
       <c r="B47" s="15" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="14" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="49" ht="32.4" customHeight="1">
       <c r="B49" s="15" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="14" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="15" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="C52" s="14" t="s">
         <v>545</v>
       </c>
-      <c r="C52" s="14" t="s">
-        <v>542</v>
-      </c>
       <c r="D52" s="14" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="53" ht="32.4" customHeight="1">
       <c r="B53" s="15" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="14" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="15" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="14" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="15" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="58" ht="32.4" customHeight="1">
       <c r="B58" s="14" t="s">
+        <v>571</v>
+      </c>
+      <c r="C58" s="14" t="s">
         <v>568</v>
       </c>
-      <c r="C58" s="14" t="s">
-        <v>565</v>
-      </c>
       <c r="D58" s="14" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="59" ht="32.4" customHeight="1">
       <c r="B59" s="15" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D59" s="15" t="s">
+        <v>576</v>
+      </c>
+      <c r="E59" s="15" t="s">
         <v>573</v>
-      </c>
-      <c r="E59" s="15" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="60" ht="32.4" customHeight="1">
       <c r="B60" s="14" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="15" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="B62" s="14" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="B63" s="15" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="64" ht="32.4" customHeight="1">
       <c r="B64" s="14" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="65" ht="32.4" customHeight="1">
       <c r="B65" s="15" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="66" ht="32.4" customHeight="1">
       <c r="B66" s="14" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="B67" s="15" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="68" ht="32.4" customHeight="1">
       <c r="B68" s="14" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="69" ht="32.4" customHeight="1">
       <c r="B69" s="15" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="70" ht="32.4" customHeight="1">
       <c r="B70" s="14" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="71" ht="32.4" customHeight="1">
       <c r="B71" s="15" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="B72" s="14" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="73" ht="6" customHeight="1"/>
     <row r="74" ht="8" customHeight="1"/>
     <row r="75" ht="24" customHeight="1">
       <c r="B75" s="4" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -8649,133 +8674,133 @@
     <row r="76" ht="4" customHeight="1"/>
     <row r="77" ht="18" customHeight="1">
       <c r="B77" s="13" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="E77" s="13"/>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="B78" s="14" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="E78" s="14"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="B79" s="15" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E79" s="15"/>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="B80" s="14" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E80" s="14"/>
     </row>
     <row r="81" ht="32.4" customHeight="1">
       <c r="B81" s="15" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E81" s="15"/>
     </row>
     <row r="82" ht="32.4" customHeight="1">
       <c r="B82" s="14" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="E82" s="14"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="B83" s="15" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="E83" s="15"/>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="B84" s="14" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E84" s="14"/>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="B85" s="15" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="E85" s="15"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="B86" s="14" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E86" s="14"/>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="B87" s="15" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="E87" s="15"/>
     </row>
@@ -8783,7 +8808,7 @@
     <row r="89" ht="8" customHeight="1"/>
     <row r="90" ht="24" customHeight="1">
       <c r="B90" s="4" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -8792,7 +8817,7 @@
     <row r="91" ht="4" customHeight="1"/>
     <row r="92" ht="18" customHeight="1">
       <c r="B92" s="7" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
@@ -8800,7 +8825,7 @@
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="B93" s="7" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
@@ -8808,7 +8833,7 @@
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="B94" s="7" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
@@ -8816,7 +8841,7 @@
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="B95" s="7" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
@@ -8914,7 +8939,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -8922,42 +8947,42 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8" ht="6" customHeight="1"/>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="24" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -8965,7 +8990,7 @@
     <row r="11" ht="4" customHeight="1"/>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="6" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -8973,49 +8998,49 @@
     <row r="13" ht="6" customHeight="1"/>
     <row r="14" ht="16.2" customHeight="1">
       <c r="B14" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
     </row>
     <row r="15" ht="16.2" customHeight="1">
       <c r="B15" s="10" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
     </row>
     <row r="16" ht="16.2" customHeight="1">
       <c r="B16" s="10" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
     </row>
     <row r="17" ht="16.2" customHeight="1">
       <c r="B17" s="10" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
     </row>
     <row r="18" ht="16.2" customHeight="1">
       <c r="B18" s="10" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
     </row>
     <row r="19" ht="16.2" customHeight="1">
       <c r="B19" s="10" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
     </row>
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="11" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -9023,28 +9048,28 @@
     <row r="21" ht="6" customHeight="1"/>
     <row r="22" ht="16.2" customHeight="1">
       <c r="B22" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
     </row>
     <row r="23" ht="16.2" customHeight="1">
       <c r="B23" s="10" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
     </row>
     <row r="24" ht="16.2" customHeight="1">
       <c r="B24" s="10" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
     </row>
     <row r="25" ht="16.2" customHeight="1">
       <c r="B25" s="11" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
@@ -9052,141 +9077,141 @@
     <row r="26" ht="6" customHeight="1"/>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="14" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="14" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="15" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="14" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="15" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="15" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="36" ht="32.4" customHeight="1">
       <c r="B36" s="14" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="15" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="38" ht="32.4" customHeight="1">
       <c r="B38" s="14" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="39" ht="6" customHeight="1"/>
     <row r="40" ht="8" customHeight="1"/>
     <row r="41" ht="24" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -9194,163 +9219,163 @@
     <row r="42" ht="4" customHeight="1"/>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="13" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="14" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="15" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="14" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="15" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="14" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="15" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
     </row>
     <row r="50" ht="32.4" customHeight="1">
       <c r="B50" s="14" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="15" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="14" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="15" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="14" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="15" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="14" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="57" ht="6" customHeight="1"/>
     <row r="58" ht="8" customHeight="1"/>
     <row r="59" ht="24" customHeight="1">
       <c r="B59" s="4" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
@@ -9358,21 +9383,21 @@
     <row r="60" ht="4" customHeight="1"/>
     <row r="61" ht="16.2" customHeight="1">
       <c r="B61" s="9" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
     </row>
     <row r="62" ht="16.2" customHeight="1">
       <c r="B62" s="10" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
     </row>
     <row r="63" ht="16.2" customHeight="1">
       <c r="B63" s="11" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
@@ -9380,14 +9405,14 @@
     <row r="64" ht="6" customHeight="1"/>
     <row r="65" ht="16.2" customHeight="1">
       <c r="B65" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
     </row>
     <row r="66" ht="30.6" customHeight="1">
       <c r="B66" s="11" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
@@ -9395,14 +9420,14 @@
     <row r="67" ht="6" customHeight="1"/>
     <row r="68" ht="18" customHeight="1">
       <c r="B68" s="7" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="B69" s="7" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
@@ -9411,7 +9436,7 @@
     <row r="71" ht="8" customHeight="1"/>
     <row r="72" ht="24" customHeight="1">
       <c r="B72" s="4" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -9419,21 +9444,21 @@
     <row r="73" ht="4" customHeight="1"/>
     <row r="74" ht="18" customHeight="1">
       <c r="B74" s="7" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="B75" s="7" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="B76" s="7" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
@@ -9502,7 +9527,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -9510,7 +9535,7 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="6" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -9518,75 +9543,75 @@
     <row r="6" ht="6" customHeight="1"/>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="13" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
     </row>
     <row r="13" ht="6" customHeight="1"/>
     <row r="14" ht="8" customHeight="1"/>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -9594,49 +9619,49 @@
     <row r="16" ht="4" customHeight="1"/>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="7" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="7" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="7" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="7" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="7" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="7" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="7" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -9645,7 +9670,7 @@
     <row r="25" ht="8" customHeight="1"/>
     <row r="26" ht="24" customHeight="1">
       <c r="B26" s="4" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -9653,53 +9678,53 @@
     <row r="27" ht="4" customHeight="1"/>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="13" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="14" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="15" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
     </row>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="14" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
     </row>
     <row r="32" ht="6" customHeight="1"/>
     <row r="33" ht="8" customHeight="1"/>
     <row r="34" ht="24" customHeight="1">
       <c r="B34" s="4" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -9707,35 +9732,35 @@
     <row r="35" ht="4" customHeight="1"/>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="9" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="16.2" customHeight="1">
       <c r="B38" s="10" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="11" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
@@ -9744,7 +9769,7 @@
     <row r="42" ht="8" customHeight="1"/>
     <row r="43" ht="24" customHeight="1">
       <c r="B43" s="4" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -9752,21 +9777,21 @@
     <row r="44" ht="4" customHeight="1"/>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="7" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="7" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="7" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -9775,7 +9800,7 @@
     <row r="49" ht="8" customHeight="1"/>
     <row r="50" ht="24" customHeight="1">
       <c r="B50" s="4" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -9783,7 +9808,7 @@
     <row r="51" ht="4" customHeight="1"/>
     <row r="52" ht="46.8" customHeight="1">
       <c r="B52" s="6" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>

--- a/docs/JMeter_Usage_Guide.xlsx
+++ b/docs/JMeter_Usage_Guide.xlsx
@@ -217,7 +217,7 @@
     <t>input/openapi_config.csv</t>
   </si>
   <si>
-    <t>OpenAPI 定義（.json）から生成する場合の設定（接続先・HTTP ヘッダ・アクセストークン）。generate の -c / -OpenApiConfig で指定</t>
+    <t>OpenAPI 定義（.json）から生成する場合の設定（接続先・HTTP ヘッダ・アクセストークン・定義の変数 ${public_base_url} / ${name_prefix} の値）。generate の -c / -OpenApiConfig で指定</t>
   </si>
   <si>
     <t>output/api_test.jmx</t>
@@ -472,7 +472,7 @@
     <t>・api_definition_settings.csv（CSV 形式：設定）</t>
   </si>
   <si>
-    <t>・openapi_config.csv（CSV 形式：OpenAPI 定義から生成する場合の接続先・HTTP ヘッダ・アクセストークン。generate の -c / -OpenApiConfig で指定）</t>
+    <t>・openapi_config.csv（CSV 形式：OpenAPI 定義から生成する場合の接続先・HTTP ヘッダ・アクセストークン・定義の変数 ${public_base_url} / ${name_prefix} の値。generate の -c / -OpenApiConfig で指定）</t>
   </si>
   <si>
     <t>手順2：API 定義を記入する</t>
@@ -5423,7 +5423,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" ht="32.4" customHeight="1">
+    <row r="21" ht="46.8" customHeight="1">
       <c r="B21" s="14" t="s">
         <v>63</v>
       </c>
@@ -6117,7 +6117,7 @@
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="32.4" customHeight="1">
       <c r="B14" s="7" t="s">
         <v>149</v>
       </c>

--- a/docs/JMeter_Usage_Guide.xlsx
+++ b/docs/JMeter_Usage_Guide.xlsx
@@ -23,12 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="1088">
   <si>
     <t>JMeter APIテスト 利用方法</t>
   </si>
   <si>
-    <t>対象: Apache JMeter 5.6.3 ／ RHEL 9.8 ／ Windows 11 ／ ツール: jmeter_api_tool v1.0.0（2026-10-24 出力）</t>
+    <t>対象: Apache JMeter 5.6.3 ／ RHEL 9.8 ／ Windows 11 ／ ツール: jmeter_api_tool v1.1.0（2026-10-25 出力）</t>
   </si>
   <si>
     <t>本書は、REST API の定義（URL・HTTPメソッド・クエリパラメータ・ヘッダ・リクエストボディ）を Excel または CSV に記入し、JMeter のテスト計画ファイル（JMX）を自動生成して実行し、結果を確認するまでの手順をまとめたものです。</t>
@@ -160,6 +160,9 @@
     <t>・Excel / CSV に記入した API 定義から、JMeter 5.6.3 用の JMX ファイルを自動生成します。</t>
   </si>
   <si>
+    <t>・curl コマンドを解析し、api_definition.xlsx の空白行と api_definition.csv に 1 行追加します。</t>
+  </si>
+  <si>
     <t>・生成される JMX には、API テストでよく使う要素（待機タイマ、連番・乱数、CSV / Excel データ読込、クッキー、前処理・後処理、正規表現 / JSON 抽出、応答の検証、結果出力）があらかじめ組み込まれています。</t>
   </si>
   <si>
@@ -169,6 +172,15 @@
     <t>・実行結果は JTL（CSV）、HTML レポート、jmeter.log、結果ログ（api_result.log）、エラー詳細（error_detail.xml）に出力されます。</t>
   </si>
   <si>
+    <t>・generate は JMX と同じフォルダに、Linux の JMeter CLI 実行コマンドと各パラメータの説明（*_cli.txt）を出力します。</t>
+  </si>
+  <si>
+    <t>・既存の JMX を -t で指定すると、新規の JMX は作らず、Excel / CSV / OpenAPI の定義との差分だけをその JMX へ更新します。更新箇所は画面と *_update.txt に表示します。手で追加した要素は残します。--diff（PowerShell は -Diff）を付けると、JMX は書き換えずに差分だけを表示します。</t>
+  </si>
+  <si>
+    <t>・cli コマンドは、既存の JMX から Linux 用 CLI 手順（*_cli.txt）を作り直します。手順書には環境変数、nohup によるバックグラウンド実行、jmeter -g によるレポート再生成も含みます。</t>
+  </si>
+  <si>
     <t>・生成される要素の名前には [必須] / [任意] を付けています。[任意] の要素は JMeter GUI で右クリック →「削除」するだけで、他の要素に影響を与えずに取り除けます。</t>
   </si>
   <si>
@@ -475,6 +487,39 @@
     <t>・openapi_config.csv（CSV 形式：OpenAPI 定義から生成する場合の接続先・HTTP ヘッダ・アクセストークン・定義の変数 ${public_base_url} / ${name_prefix} の値。generate の -c / -OpenApiConfig で指定）</t>
   </si>
   <si>
+    <t>curl コマンドから API 定義を作る</t>
+  </si>
+  <si>
+    <t>curl コマンドをファイルに書いて実行すると、既存の api_definition.xlsx の最初の空白行と、同じ名前の api_definition.csv の末尾に 1 行追加します。curl 1 件が 1 行です。既存の API 行と「設定」シートは変更しません。ファイルには複数コマンドを書けます。行継続（\、^、バッククォート）と引用符に対応します。</t>
+  </si>
+  <si>
+    <t>./jmeter_api_tool.sh curl -i requests.curl -o input/api_definition.xlsx</t>
+  </si>
+  <si>
+    <t>./jmeter_api_tool.sh generate -i input/api_definition.xlsx</t>
+  </si>
+  <si>
+    <t>.\jmeter_api_tool.bat curl -i requests.curl -o input\api_definition.xlsx</t>
+  </si>
+  <si>
+    <t>.\jmeter_api_tool.bat generate -i input\api_definition.xlsx</t>
+  </si>
+  <si>
+    <t>・URL の ? 以降は「クエリパラメータ」列に分けます。-G と --data-urlencode もクエリになります。</t>
+  </si>
+  <si>
+    <t>・-d / --json / -F は本文とボディ形式にします。-d で Content-Type を書いていない場合は、curl と同じ application/x-www-form-urlencoded として取り込みます（JSON に見える文字列でも application/json にはしません）。</t>
+  </si>
+  <si>
+    <t>・もう一度実行すると、その続きの空白行（CSV は末尾）にさらに 1 行追加します。</t>
+  </si>
+  <si>
+    <t>・ファイルが無い場合は、テンプレートの記入例の次の空白行から追加します。</t>
+  </si>
+  <si>
+    <t>・期待ステータスは空欄です。必要なら記入してから generate してください。</t>
+  </si>
+  <si>
     <t>手順2：API 定義を記入する</t>
   </si>
   <si>
@@ -496,18 +541,12 @@
     <t>手順3：JMX を生成する</t>
   </si>
   <si>
-    <t>./jmeter_api_tool.sh generate -i input/api_definition.xlsx</t>
-  </si>
-  <si>
     <t>./jmeter_api_tool.sh generate -i input/api_definition.csv -s input/api_definition_settings.csv</t>
   </si>
   <si>
     <t># Windows 11</t>
   </si>
   <si>
-    <t>.\jmeter_api_tool.bat generate -i input\api_definition.xlsx</t>
-  </si>
-  <si>
     <t>.\jmeter_api_tool.bat generate -i input\api_definition.csv -s input\api_definition_settings.csv</t>
   </si>
   <si>
@@ -526,7 +565,7 @@
     <t>-InputFile（-i）</t>
   </si>
   <si>
-    <t>入力ファイル（.xlsx / .csv）。必須</t>
+    <t>入力ファイル（.xlsx / .csv / .json）。必須</t>
   </si>
   <si>
     <t>-s ファイル</t>
@@ -574,6 +613,15 @@
     <t>サンプルデータ（data/testdata.csv / .xlsx）が既にあっても上書きする</t>
   </si>
   <si>
+    <t>-t ファイル</t>
+  </si>
+  <si>
+    <t>-Jmx（-t）</t>
+  </si>
+  <si>
+    <t>既存の JMX。指定すると新規作成せず、Excel / CSV / OpenAPI の定義との差分だけをそのファイルへ更新する。更新箇所は画面と *_update.txt に表示する。--split とは同時に使えない</t>
+  </si>
+  <si>
     <t>生成されるファイル</t>
   </si>
   <si>
@@ -583,13 +631,40 @@
     <t>output/出力JMXファイル名</t>
   </si>
   <si>
-    <t>生成された JMX。同名のファイルがある場合は「.日時.bak」を付けて退避してから作成します</t>
+    <t>生成された JMX。同名のファイルがある場合は「.日時.bak」を付けて退避してから作成します。-t で既存の JMX を指定したときは、退避せず差分だけを更新します</t>
+  </si>
+  <si>
+    <t>output/出力JMXファイル名_cli.txt</t>
+  </si>
+  <si>
+    <t>Linux サーバで JMeter CLI を実行するコマンドと、各パラメータの説明。JMX と同じフォルダに出力する</t>
+  </si>
+  <si>
+    <t>output/出力JMXファイル名_update.txt</t>
+  </si>
+  <si>
+    <t>-t で既存の JMX を更新したときの更新箇所。差分が無いときも出力する</t>
   </si>
   <si>
     <t>CSV データ読込用のサンプル（ファイルが無い場合のみ作成）</t>
   </si>
   <si>
     <t>Excel データ読込用のサンプル（ファイルが無い場合のみ作成）</t>
+  </si>
+  <si>
+    <t>既存の JMX を更新する場合は、-t にそのファイルを指定します。Excel、CSV、OpenAPI のどれからでも同じです。新しい JMX は作らず、定義と違う箇所だけを書き換えます。更新・追加・削除した箇所は画面に表示し、JMX と同じフォルダの *_update.txt にも書きます。名前が [必須] / [任意] で始まらない要素、および APIxx ではないサンプラは、手で追加したものとして残します。差分が無いときは JMX を書き換えません。</t>
+  </si>
+  <si>
+    <t>./jmeter_api_tool.sh generate -i input/api_definition.xlsx -t output/api_test.jmx</t>
+  </si>
+  <si>
+    <t>./jmeter_api_tool.sh generate -i openapi.json -t output/api_test.jmx</t>
+  </si>
+  <si>
+    <t>.\jmeter_api_tool.bat generate -i input\api_definition.xlsx -t output\api_test.jmx</t>
+  </si>
+  <si>
+    <t>.\jmeter_api_tool.bat generate -i openapi.json -t output\api_test.jmx</t>
   </si>
   <si>
     <t>手順4：JMeter GUI で確認・調整する</t>
@@ -1418,7 +1493,7 @@
     <t>・「有効」を N にした API は、生成はされますが無効化された状態になります。</t>
   </si>
   <si>
-    <t>・GET / DELETE のクエリパラメータは HTTP リクエストの「Parameters」タブに設定されます。POST / PUT / PATCH の場合は URL のパスに付与されます（値は UTF-8 で URL エンコード。${...} の部分はそのまま）。</t>
+    <t>・GET / DELETE / HEAD / OPTIONS のクエリパラメータは HTTP リクエストの「Parameters」タブに設定されます。POST / PUT / PATCH の場合は URL のパスに付与されます（値は UTF-8 で URL エンコード。${...} の部分はそのまま）。</t>
   </si>
   <si>
     <t>・既に URL エンコード済みの値（%E3%83%86 など）は、二重にエンコードしないよう自動で判定します。</t>
@@ -2052,12 +2127,6 @@
   </si>
   <si>
     <t>.\jmeter_api_tool.bat run -t output\api_test.jmx -Threads 50 -Loops 200 -Prop HOST=stg.example.com -Heap 2g</t>
-  </si>
-  <si>
-    <t>-t ファイル</t>
-  </si>
-  <si>
-    <t>-Jmx（-t）</t>
   </si>
   <si>
     <t>実行する JMX。必須</t>
@@ -3839,50 +3908,50 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>807</v>
+        <v>830</v>
       </c>
       <c r="C3" s="4"/>
     </row>
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="16.2" customHeight="1">
       <c r="B5" s="9" t="s">
-        <v>808</v>
+        <v>831</v>
       </c>
       <c r="C5" s="9"/>
     </row>
     <row r="6" ht="16.2" customHeight="1">
       <c r="B6" s="10" t="s">
-        <v>809</v>
+        <v>832</v>
       </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" ht="16.2" customHeight="1">
       <c r="B7" s="10" t="s">
-        <v>810</v>
+        <v>833</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" ht="16.2" customHeight="1">
       <c r="B8" s="10" t="s">
-        <v>811</v>
+        <v>834</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" ht="16.2" customHeight="1">
       <c r="B9" s="10" t="s">
-        <v>812</v>
+        <v>835</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" ht="16.2" customHeight="1">
       <c r="B10" s="10" t="s">
-        <v>813</v>
+        <v>836</v>
       </c>
       <c r="C10" s="10"/>
     </row>
     <row r="11" ht="16.2" customHeight="1">
       <c r="B11" s="11" t="s">
-        <v>814</v>
+        <v>837</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -3890,55 +3959,55 @@
     <row r="13" ht="8" customHeight="1"/>
     <row r="14" ht="24" customHeight="1">
       <c r="B14" s="4" t="s">
-        <v>815</v>
+        <v>838</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15" ht="4" customHeight="1"/>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="13" t="s">
-        <v>816</v>
+        <v>839</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>817</v>
+        <v>840</v>
       </c>
     </row>
     <row r="17" ht="32.4" customHeight="1">
       <c r="B17" s="14" t="s">
-        <v>818</v>
+        <v>841</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>819</v>
+        <v>842</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="15" t="s">
-        <v>820</v>
+        <v>843</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>821</v>
+        <v>844</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="14" t="s">
-        <v>822</v>
+        <v>845</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>823</v>
+        <v>846</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>824</v>
+        <v>847</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>825</v>
+        <v>848</v>
       </c>
     </row>
     <row r="21" ht="6" customHeight="1"/>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="6" t="s">
-        <v>826</v>
+        <v>849</v>
       </c>
       <c r="C22" s="6"/>
     </row>
@@ -3946,14 +4015,14 @@
     <row r="24" ht="8" customHeight="1"/>
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="4" t="s">
-        <v>827</v>
+        <v>850</v>
       </c>
       <c r="C25" s="4"/>
     </row>
     <row r="26" ht="4" customHeight="1"/>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="13" t="s">
-        <v>828</v>
+        <v>851</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>6</v>
@@ -3961,104 +4030,104 @@
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="14" t="s">
-        <v>829</v>
+        <v>852</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>830</v>
+        <v>853</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>831</v>
+        <v>854</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>832</v>
+        <v>855</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="14" t="s">
-        <v>833</v>
+        <v>856</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="15" t="s">
-        <v>835</v>
+        <v>858</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>836</v>
+        <v>859</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="14" t="s">
-        <v>837</v>
+        <v>860</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>838</v>
+        <v>861</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="15" t="s">
-        <v>839</v>
+        <v>862</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>840</v>
+        <v>863</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="14" t="s">
-        <v>841</v>
+        <v>864</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>842</v>
+        <v>865</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="15" t="s">
-        <v>843</v>
+        <v>866</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>844</v>
+        <v>867</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="14" t="s">
-        <v>845</v>
+        <v>868</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>846</v>
+        <v>869</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="15" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>847</v>
+        <v>870</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="14" t="s">
-        <v>848</v>
+        <v>871</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>849</v>
+        <v>872</v>
       </c>
     </row>
     <row r="39" ht="6" customHeight="1"/>
     <row r="40" ht="8" customHeight="1"/>
     <row r="41" ht="24" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>850</v>
+        <v>873</v>
       </c>
       <c r="C41" s="4"/>
     </row>
     <row r="42" ht="4" customHeight="1"/>
     <row r="43" ht="46.8" customHeight="1">
       <c r="B43" s="6" t="s">
-        <v>851</v>
+        <v>874</v>
       </c>
       <c r="C43" s="6"/>
     </row>
@@ -4066,14 +4135,14 @@
     <row r="45" ht="8" customHeight="1"/>
     <row r="46" ht="24" customHeight="1">
       <c r="B46" s="4" t="s">
-        <v>852</v>
+        <v>875</v>
       </c>
       <c r="C46" s="4"/>
     </row>
     <row r="47" ht="4" customHeight="1"/>
     <row r="48" ht="32.4" customHeight="1">
       <c r="B48" s="6" t="s">
-        <v>853</v>
+        <v>876</v>
       </c>
       <c r="C48" s="6"/>
     </row>
@@ -4081,26 +4150,26 @@
     <row r="50" ht="8" customHeight="1"/>
     <row r="51" ht="24" customHeight="1">
       <c r="B51" s="4" t="s">
-        <v>854</v>
+        <v>877</v>
       </c>
       <c r="C51" s="4"/>
     </row>
     <row r="52" ht="4" customHeight="1"/>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="7" t="s">
-        <v>855</v>
+        <v>878</v>
       </c>
       <c r="C53" s="7"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="7" t="s">
-        <v>856</v>
+        <v>879</v>
       </c>
       <c r="C54" s="7"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="7" t="s">
-        <v>857</v>
+        <v>880</v>
       </c>
       <c r="C55" s="7"/>
     </row>
@@ -4160,7 +4229,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>858</v>
+        <v>881</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -4168,10 +4237,10 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>626</v>
+        <v>651</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>6</v>
@@ -4179,97 +4248,97 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>859</v>
+        <v>882</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>860</v>
+        <v>883</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>861</v>
+        <v>884</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>862</v>
+        <v>885</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>863</v>
+        <v>886</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>864</v>
+        <v>887</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>865</v>
+        <v>888</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>866</v>
+        <v>889</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>867</v>
+        <v>890</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>868</v>
+        <v>891</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>869</v>
+        <v>892</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>870</v>
+        <v>893</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>871</v>
+        <v>894</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>872</v>
+        <v>895</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>873</v>
+        <v>896</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="15" t="s">
-        <v>874</v>
+        <v>897</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>875</v>
+        <v>898</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>876</v>
+        <v>899</v>
       </c>
     </row>
     <row r="14" ht="6" customHeight="1"/>
     <row r="15" ht="8" customHeight="1"/>
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="4" t="s">
-        <v>877</v>
+        <v>900</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -4277,152 +4346,152 @@
     <row r="17" ht="4" customHeight="1"/>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="13" t="s">
-        <v>878</v>
+        <v>901</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>879</v>
+        <v>902</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="14" t="s">
-        <v>880</v>
+        <v>903</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>881</v>
+        <v>904</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>882</v>
+        <v>905</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>883</v>
+        <v>906</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>884</v>
+        <v>907</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>885</v>
+        <v>908</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="14" t="s">
-        <v>886</v>
+        <v>909</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>887</v>
+        <v>910</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>888</v>
+        <v>911</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="15" t="s">
-        <v>889</v>
+        <v>912</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>890</v>
+        <v>913</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>891</v>
+        <v>914</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="14" t="s">
-        <v>892</v>
+        <v>915</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>893</v>
+        <v>916</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>894</v>
+        <v>917</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="15" t="s">
-        <v>895</v>
+        <v>918</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>896</v>
+        <v>919</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>897</v>
+        <v>920</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="14" t="s">
-        <v>898</v>
+        <v>921</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>899</v>
+        <v>922</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>900</v>
+        <v>923</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="15" t="s">
-        <v>901</v>
+        <v>924</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>902</v>
+        <v>925</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>903</v>
+        <v>926</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="14" t="s">
-        <v>904</v>
+        <v>927</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>905</v>
+        <v>928</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>906</v>
+        <v>929</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="15" t="s">
-        <v>907</v>
+        <v>930</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>908</v>
+        <v>931</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>909</v>
+        <v>932</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="14" t="s">
-        <v>910</v>
+        <v>933</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>911</v>
+        <v>934</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>912</v>
+        <v>935</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="15" t="s">
-        <v>913</v>
+        <v>936</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>914</v>
+        <v>937</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>915</v>
+        <v>938</v>
       </c>
     </row>
     <row r="31" ht="6" customHeight="1"/>
     <row r="32" ht="8" customHeight="1"/>
     <row r="33" ht="24" customHeight="1">
       <c r="B33" s="4" t="s">
-        <v>916</v>
+        <v>939</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -4430,105 +4499,105 @@
     <row r="34" ht="4" customHeight="1"/>
     <row r="35" ht="16.2" customHeight="1">
       <c r="B35" s="9" t="s">
-        <v>917</v>
+        <v>940</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
     </row>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="10" t="s">
-        <v>918</v>
+        <v>941</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>919</v>
+        <v>942</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="16.2" customHeight="1">
       <c r="B38" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>920</v>
+        <v>943</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="10" t="s">
-        <v>921</v>
+        <v>944</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="16.2" customHeight="1">
       <c r="B41" s="10" t="s">
-        <v>922</v>
+        <v>945</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
     </row>
     <row r="42" ht="16.2" customHeight="1">
       <c r="B42" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C42" s="10"/>
       <c r="D42" s="10"/>
     </row>
     <row r="43" ht="16.2" customHeight="1">
       <c r="B43" s="10" t="s">
-        <v>923</v>
+        <v>946</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
     </row>
     <row r="44" ht="16.2" customHeight="1">
       <c r="B44" s="10" t="s">
-        <v>924</v>
+        <v>947</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
     </row>
     <row r="45" ht="16.2" customHeight="1">
       <c r="B45" s="10" t="s">
-        <v>925</v>
+        <v>948</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
     </row>
     <row r="46" ht="16.2" customHeight="1">
       <c r="B46" s="10" t="s">
-        <v>926</v>
+        <v>949</v>
       </c>
       <c r="C46" s="10"/>
       <c r="D46" s="10"/>
     </row>
     <row r="47" ht="16.2" customHeight="1">
       <c r="B47" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="10"/>
     </row>
     <row r="48" ht="16.2" customHeight="1">
       <c r="B48" s="10" t="s">
-        <v>927</v>
+        <v>950</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="10"/>
     </row>
     <row r="49" ht="16.2" customHeight="1">
       <c r="B49" s="11" t="s">
-        <v>928</v>
+        <v>951</v>
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
@@ -4536,21 +4605,21 @@
     <row r="50" ht="6" customHeight="1"/>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="7" t="s">
-        <v>929</v>
+        <v>952</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="7" t="s">
-        <v>930</v>
+        <v>953</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="7" t="s">
-        <v>931</v>
+        <v>954</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -4559,7 +4628,7 @@
     <row r="55" ht="8" customHeight="1"/>
     <row r="56" ht="24" customHeight="1">
       <c r="B56" s="4" t="s">
-        <v>932</v>
+        <v>955</v>
       </c>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
@@ -4567,60 +4636,60 @@
     <row r="57" ht="4" customHeight="1"/>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="13" t="s">
-        <v>933</v>
+        <v>956</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>934</v>
+        <v>957</v>
       </c>
       <c r="D58" s="13"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="14" t="s">
-        <v>935</v>
+        <v>958</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>936</v>
+        <v>959</v>
       </c>
       <c r="D59" s="14"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="15" t="s">
-        <v>937</v>
+        <v>960</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>938</v>
+        <v>961</v>
       </c>
       <c r="D60" s="15"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="14" t="s">
-        <v>939</v>
+        <v>962</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>940</v>
+        <v>963</v>
       </c>
       <c r="D61" s="14"/>
     </row>
     <row r="62" ht="32.4" customHeight="1">
       <c r="B62" s="15" t="s">
-        <v>941</v>
+        <v>964</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>942</v>
+        <v>965</v>
       </c>
       <c r="D62" s="15"/>
     </row>
     <row r="63" ht="6" customHeight="1"/>
     <row r="64" ht="18" customHeight="1">
       <c r="B64" s="7" t="s">
-        <v>943</v>
+        <v>966</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="B65" s="7" t="s">
-        <v>944</v>
+        <v>967</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -4629,7 +4698,7 @@
     <row r="67" ht="8" customHeight="1"/>
     <row r="68" ht="24" customHeight="1">
       <c r="B68" s="4" t="s">
-        <v>945</v>
+        <v>968</v>
       </c>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
@@ -4637,55 +4706,55 @@
     <row r="69" ht="4" customHeight="1"/>
     <row r="70" ht="18" customHeight="1">
       <c r="B70" s="13" t="s">
-        <v>933</v>
+        <v>956</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>946</v>
+        <v>969</v>
       </c>
       <c r="D70" s="13"/>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="B71" s="14" t="s">
-        <v>947</v>
+        <v>970</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>948</v>
+        <v>971</v>
       </c>
       <c r="D71" s="14"/>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="B72" s="15" t="s">
-        <v>949</v>
+        <v>972</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>950</v>
+        <v>973</v>
       </c>
       <c r="D72" s="15"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="B73" s="14" t="s">
-        <v>951</v>
+        <v>974</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>952</v>
+        <v>975</v>
       </c>
       <c r="D73" s="14"/>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="B74" s="15" t="s">
-        <v>953</v>
+        <v>976</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>954</v>
+        <v>977</v>
       </c>
       <c r="D74" s="15"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="B75" s="14" t="s">
-        <v>955</v>
+        <v>978</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>956</v>
+        <v>979</v>
       </c>
       <c r="D75" s="14"/>
     </row>
@@ -4762,200 +4831,200 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="13" t="s">
-        <v>957</v>
+        <v>980</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>958</v>
+        <v>981</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>959</v>
+        <v>982</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="B4" s="14" t="s">
-        <v>960</v>
+        <v>983</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>961</v>
+        <v>984</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>962</v>
+        <v>985</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="15" t="s">
-        <v>963</v>
+        <v>986</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>964</v>
+        <v>987</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>965</v>
+        <v>988</v>
       </c>
     </row>
     <row r="6" ht="32.4" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>966</v>
+        <v>989</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>967</v>
+        <v>990</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>968</v>
+        <v>991</v>
       </c>
     </row>
     <row r="7" ht="32.4" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>969</v>
+        <v>992</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>970</v>
+        <v>993</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>971</v>
+        <v>994</v>
       </c>
     </row>
     <row r="8" ht="32.4" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>972</v>
+        <v>995</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>973</v>
+        <v>996</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>974</v>
+        <v>997</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>975</v>
+        <v>998</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>976</v>
+        <v>999</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>977</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10" ht="32.4" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>978</v>
+        <v>1001</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>979</v>
+        <v>1002</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>980</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="11" ht="32.4" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>981</v>
+        <v>1004</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>982</v>
+        <v>1005</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>983</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>984</v>
+        <v>1007</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>985</v>
+        <v>1008</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>986</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="13" ht="32.4" customHeight="1">
       <c r="B13" s="15" t="s">
-        <v>987</v>
+        <v>1010</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>988</v>
+        <v>1011</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>989</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="14" ht="32.4" customHeight="1">
       <c r="B14" s="14" t="s">
-        <v>990</v>
+        <v>1013</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>991</v>
+        <v>1014</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>992</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="15" ht="32.4" customHeight="1">
       <c r="B15" s="15" t="s">
-        <v>993</v>
+        <v>1016</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>994</v>
+        <v>1017</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>995</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="16" ht="32.4" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>996</v>
+        <v>1019</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>997</v>
+        <v>1020</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>998</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="17" ht="32.4" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>999</v>
+        <v>1022</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1000</v>
+        <v>1023</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>1001</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>1002</v>
+        <v>1025</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1003</v>
+        <v>1026</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>1004</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="19" ht="32.4" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>1005</v>
+        <v>1028</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1006</v>
+        <v>1029</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>1007</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="20" ht="32.4" customHeight="1">
       <c r="B20" s="14" t="s">
-        <v>1008</v>
+        <v>1031</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1009</v>
+        <v>1032</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>1010</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="21" ht="6" customHeight="1"/>
@@ -4997,7 +5066,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>1011</v>
+        <v>1034</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -5006,93 +5075,93 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>1012</v>
+        <v>1035</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>1013</v>
+        <v>1036</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1014</v>
+        <v>1037</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" ht="32.4" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>1015</v>
+        <v>1038</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1016</v>
+        <v>1039</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1017</v>
+        <v>1040</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1018</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="7" ht="46.8" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>1019</v>
+        <v>1042</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>1020</v>
+        <v>1043</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>1021</v>
+        <v>1044</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>1022</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="8" ht="32.4" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>1023</v>
+        <v>1046</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1024</v>
+        <v>1047</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1025</v>
+        <v>1048</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1026</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>1027</v>
+        <v>1050</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>1028</v>
+        <v>1051</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>1029</v>
+        <v>1052</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>1030</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>1031</v>
+        <v>1054</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>1032</v>
+        <v>1055</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1033</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="11" ht="6" customHeight="1"/>
     <row r="12" ht="8" customHeight="1"/>
     <row r="13" ht="24" customHeight="1">
       <c r="B13" s="4" t="s">
-        <v>1034</v>
+        <v>1057</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -5101,170 +5170,170 @@
     <row r="14" ht="4" customHeight="1"/>
     <row r="15" ht="18" customHeight="1">
       <c r="B15" s="13" t="s">
-        <v>1035</v>
+        <v>1058</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>1036</v>
+        <v>1059</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>1037</v>
+        <v>1060</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>676</v>
+        <v>196</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1038</v>
+        <v>1061</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>1039</v>
+        <v>1062</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1040</v>
+        <v>1063</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>1041</v>
+        <v>1064</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1042</v>
+        <v>1065</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="14" t="s">
-        <v>1043</v>
+        <v>1066</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1044</v>
+        <v>1067</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="15" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1045</v>
+        <v>1068</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="14" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>1046</v>
+        <v>1069</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="15" t="s">
-        <v>1047</v>
+        <v>1070</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>1048</v>
+        <v>1071</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="14" t="s">
-        <v>1049</v>
+        <v>1072</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>1050</v>
+        <v>1073</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="15" t="s">
-        <v>1051</v>
+        <v>1074</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>1052</v>
+        <v>1075</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="14" t="s">
-        <v>1053</v>
+        <v>1076</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>1054</v>
+        <v>1077</v>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="15" t="s">
-        <v>1055</v>
+        <v>1078</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>1056</v>
+        <v>1079</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="14" t="s">
-        <v>1057</v>
+        <v>1080</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>1058</v>
+        <v>1081</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>1059</v>
+        <v>1082</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>1060</v>
+        <v>1083</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="14" t="s">
-        <v>1061</v>
+        <v>1084</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>1062</v>
+        <v>1085</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="15" t="s">
-        <v>1063</v>
+        <v>1086</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>1064</v>
+        <v>1087</v>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="15"/>
@@ -5306,7 +5375,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -5334,7 +5403,7 @@
       </c>
       <c r="C5" s="7"/>
     </row>
-    <row r="6" ht="32.4" customHeight="1">
+    <row r="6" ht="18" customHeight="1">
       <c r="B6" s="7" t="s">
         <v>45</v>
       </c>
@@ -5358,152 +5427,152 @@
       </c>
       <c r="C9" s="7"/>
     </row>
-    <row r="10" ht="6" customHeight="1"/>
-    <row r="11" ht="8" customHeight="1"/>
-    <row r="12" ht="24" customHeight="1">
-      <c r="B12" s="4" t="s">
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" ht="4" customHeight="1"/>
-    <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="13" t="s">
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11" ht="46.8" customHeight="1">
+      <c r="B11" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C11" s="7"/>
+    </row>
+    <row r="12" ht="32.4" customHeight="1">
+      <c r="B12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="7"/>
+    </row>
+    <row r="13" ht="32.4" customHeight="1">
+      <c r="B13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="7"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="8" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1">
+      <c r="B16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" ht="4" customHeight="1"/>
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="B15" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="B16" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" ht="46.8" customHeight="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
       <c r="B21" s="14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="15" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="14" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" ht="46.8" customHeight="1">
       <c r="B25" s="14" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C28" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="27" ht="6" customHeight="1"/>
-    <row r="28" ht="8" customHeight="1"/>
-    <row r="29" ht="24" customHeight="1">
-      <c r="B29" s="4" t="s">
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="4"/>
-    </row>
-    <row r="30" ht="4" customHeight="1"/>
-    <row r="31" ht="18" customHeight="1">
-      <c r="B31" s="7" t="s">
+      <c r="C29" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C31" s="7"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="7" t="s">
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="7"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="B33" s="7" t="s">
+      <c r="C30" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="7"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="7" t="s">
+    </row>
+    <row r="31" ht="6" customHeight="1"/>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="24" customHeight="1">
+      <c r="B33" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="7"/>
-    </row>
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" ht="4" customHeight="1"/>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="7" t="s">
         <v>80</v>
@@ -5516,16 +5585,40 @@
       </c>
       <c r="C36" s="7"/>
     </row>
-    <row r="37" ht="6" customHeight="1"/>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" s="7"/>
+    </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="B38" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" s="8"/>
-    </row>
-    <row r="39" ht="6" customHeight="1"/>
+      <c r="B38" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="7"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="7"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" s="7"/>
+    </row>
+    <row r="41" ht="6" customHeight="1"/>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="8"/>
+    </row>
+    <row r="43" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="20">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
@@ -5533,15 +5626,19 @@
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B42:C42"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -5577,7 +5674,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -5586,79 +5683,79 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" ht="32.4" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" ht="32.4" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" ht="32.4" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="8" customHeight="1"/>
     <row r="12" ht="24" customHeight="1">
       <c r="B12" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -5667,7 +5764,7 @@
     <row r="13" ht="4" customHeight="1"/>
     <row r="14" ht="16.2" customHeight="1">
       <c r="B14" s="9" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -5675,7 +5772,7 @@
     </row>
     <row r="15" ht="16.2" customHeight="1">
       <c r="B15" s="10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
@@ -5683,7 +5780,7 @@
     </row>
     <row r="16" ht="16.2" customHeight="1">
       <c r="B16" s="10" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -5691,7 +5788,7 @@
     </row>
     <row r="17" ht="16.2" customHeight="1">
       <c r="B17" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -5699,7 +5796,7 @@
     </row>
     <row r="18" ht="16.2" customHeight="1">
       <c r="B18" s="10" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -5707,7 +5804,7 @@
     </row>
     <row r="19" ht="16.2" customHeight="1">
       <c r="B19" s="10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -5715,7 +5812,7 @@
     </row>
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="10" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -5723,7 +5820,7 @@
     </row>
     <row r="21" ht="16.2" customHeight="1">
       <c r="B21" s="10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -5731,7 +5828,7 @@
     </row>
     <row r="22" ht="16.2" customHeight="1">
       <c r="B22" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
@@ -5739,7 +5836,7 @@
     </row>
     <row r="23" ht="16.2" customHeight="1">
       <c r="B23" s="10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
@@ -5747,7 +5844,7 @@
     </row>
     <row r="24" ht="16.2" customHeight="1">
       <c r="B24" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
@@ -5755,7 +5852,7 @@
     </row>
     <row r="25" ht="16.2" customHeight="1">
       <c r="B25" s="10" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
@@ -5763,7 +5860,7 @@
     </row>
     <row r="26" ht="16.2" customHeight="1">
       <c r="B26" s="10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
@@ -5771,7 +5868,7 @@
     </row>
     <row r="27" ht="16.2" customHeight="1">
       <c r="B27" s="10" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
@@ -5779,7 +5876,7 @@
     </row>
     <row r="28" ht="16.2" customHeight="1">
       <c r="B28" s="10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
@@ -5787,7 +5884,7 @@
     </row>
     <row r="29" ht="16.2" customHeight="1">
       <c r="B29" s="11" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
@@ -5796,7 +5893,7 @@
     <row r="30" ht="6" customHeight="1"/>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -5804,7 +5901,7 @@
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -5812,7 +5909,7 @@
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -5822,7 +5919,7 @@
     <row r="35" ht="8" customHeight="1"/>
     <row r="36" ht="24" customHeight="1">
       <c r="B36" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -5831,7 +5928,7 @@
     <row r="37" ht="4" customHeight="1"/>
     <row r="38" ht="32.4" customHeight="1">
       <c r="B38" s="7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -5839,7 +5936,7 @@
     </row>
     <row r="39" ht="32.4" customHeight="1">
       <c r="B39" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -5847,7 +5944,7 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
@@ -5855,7 +5952,7 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -5864,7 +5961,7 @@
     <row r="42" ht="6" customHeight="1"/>
     <row r="43" ht="16.2" customHeight="1">
       <c r="B43" s="9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
@@ -5872,7 +5969,7 @@
     </row>
     <row r="44" ht="16.2" customHeight="1">
       <c r="B44" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
@@ -5880,7 +5977,7 @@
     </row>
     <row r="45" ht="16.2" customHeight="1">
       <c r="B45" s="10" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
@@ -5888,7 +5985,7 @@
     </row>
     <row r="46" ht="16.2" customHeight="1">
       <c r="B46" s="11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
@@ -5898,7 +5995,7 @@
     <row r="48" ht="8" customHeight="1"/>
     <row r="49" ht="24" customHeight="1">
       <c r="B49" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
@@ -5907,7 +6004,7 @@
     <row r="50" ht="4" customHeight="1"/>
     <row r="51" ht="32.4" customHeight="1">
       <c r="B51" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -5916,7 +6013,7 @@
     <row r="52" ht="6" customHeight="1"/>
     <row r="53" ht="16.2" customHeight="1">
       <c r="B53" s="9" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
@@ -5924,7 +6021,7 @@
     </row>
     <row r="54" ht="16.2" customHeight="1">
       <c r="B54" s="10" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
@@ -5932,7 +6029,7 @@
     </row>
     <row r="55" ht="16.2" customHeight="1">
       <c r="B55" s="10" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
@@ -5940,7 +6037,7 @@
     </row>
     <row r="56" ht="16.2" customHeight="1">
       <c r="B56" s="11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
@@ -5949,7 +6046,7 @@
     <row r="57" ht="6" customHeight="1"/>
     <row r="58" ht="16.2" customHeight="1">
       <c r="B58" s="9" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
@@ -5957,7 +6054,7 @@
     </row>
     <row r="59" ht="16.2" customHeight="1">
       <c r="B59" s="10" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
@@ -5965,7 +6062,7 @@
     </row>
     <row r="60" ht="16.2" customHeight="1">
       <c r="B60" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
@@ -5974,7 +6071,7 @@
     <row r="61" ht="6" customHeight="1"/>
     <row r="62" ht="32.4" customHeight="1">
       <c r="B62" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
@@ -5982,7 +6079,7 @@
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="B63" s="7" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -6047,7 +6144,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -6066,7 +6163,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -6074,7 +6171,7 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="16.2" customHeight="1">
       <c r="B5" s="12" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -6082,7 +6179,7 @@
     <row r="6" ht="6" customHeight="1"/>
     <row r="7" ht="16.2" customHeight="1">
       <c r="B7" s="12" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
@@ -6090,7 +6187,7 @@
     <row r="8" ht="6" customHeight="1"/>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="6" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -6098,28 +6195,28 @@
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="7" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
     </row>
     <row r="14" ht="32.4" customHeight="1">
       <c r="B14" s="7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -6128,266 +6225,416 @@
     <row r="16" ht="8" customHeight="1"/>
     <row r="17" ht="24" customHeight="1">
       <c r="B17" s="4" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
     <row r="18" ht="4" customHeight="1"/>
-    <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-    </row>
-    <row r="21" ht="32.4" customHeight="1">
-      <c r="B21" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+    <row r="19" ht="32.4" customHeight="1">
+      <c r="B19" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="16.2" customHeight="1">
+      <c r="B21" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+    </row>
+    <row r="22" ht="16.2" customHeight="1">
+      <c r="B22" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
     </row>
     <row r="23" ht="6" customHeight="1"/>
-    <row r="24" ht="32.4" customHeight="1">
-      <c r="B24" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-    </row>
-    <row r="25" ht="6" customHeight="1"/>
-    <row r="26" ht="8" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" ht="4" customHeight="1"/>
-    <row r="29" ht="16.2" customHeight="1">
-      <c r="B29" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-    </row>
-    <row r="30" ht="16.2" customHeight="1">
-      <c r="B30" s="10" t="s">
+    <row r="24" ht="16.2" customHeight="1">
+      <c r="B24" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+    </row>
+    <row r="25" ht="16.2" customHeight="1">
+      <c r="B25" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" ht="32.4" customHeight="1">
+      <c r="B28" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" ht="6" customHeight="1"/>
+    <row r="33" ht="8" customHeight="1"/>
+    <row r="34" ht="24" customHeight="1">
+      <c r="B34" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+    </row>
+    <row r="35" ht="4" customHeight="1"/>
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+    </row>
+    <row r="38" ht="32.4" customHeight="1">
+      <c r="B38" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+    </row>
+    <row r="40" ht="6" customHeight="1"/>
+    <row r="41" ht="32.4" customHeight="1">
+      <c r="B41" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+    </row>
+    <row r="42" ht="6" customHeight="1"/>
+    <row r="43" ht="8" customHeight="1"/>
+    <row r="44" ht="24" customHeight="1">
+      <c r="B44" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+    </row>
+    <row r="45" ht="4" customHeight="1"/>
+    <row r="46" ht="16.2" customHeight="1">
+      <c r="B46" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+    </row>
+    <row r="47" ht="16.2" customHeight="1">
+      <c r="B47" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-    </row>
-    <row r="31" ht="16.2" customHeight="1">
-      <c r="B31" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-    </row>
-    <row r="32" ht="6" customHeight="1"/>
-    <row r="33" ht="16.2" customHeight="1">
-      <c r="B33" s="9" t="s">
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+    </row>
+    <row r="48" ht="16.2" customHeight="1">
+      <c r="B48" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+    </row>
+    <row r="49" ht="6" customHeight="1"/>
+    <row r="50" ht="16.2" customHeight="1">
+      <c r="B50" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+    </row>
+    <row r="51" ht="16.2" customHeight="1">
+      <c r="B51" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-    </row>
-    <row r="34" ht="16.2" customHeight="1">
-      <c r="B34" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-    </row>
-    <row r="35" ht="16.2" customHeight="1">
-      <c r="B35" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-    </row>
-    <row r="36" ht="6" customHeight="1"/>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="B38" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="39" ht="32.4" customHeight="1">
-      <c r="B39" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="B40" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="41" ht="32.4" customHeight="1">
-      <c r="B41" s="15" t="s">
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+    </row>
+    <row r="52" ht="16.2" customHeight="1">
+      <c r="B52" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+    </row>
+    <row r="53" ht="6" customHeight="1"/>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="C54" s="13" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="14" t="s">
+      <c r="D54" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="C42" s="14" t="s">
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="C55" s="14" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="15" t="s">
+      <c r="D55" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="C43" s="15" t="s">
+    </row>
+    <row r="56" ht="32.4" customHeight="1">
+      <c r="B56" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="C56" s="15" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="44" ht="6" customHeight="1"/>
-    <row r="45" ht="8" customHeight="1"/>
-    <row r="46" ht="24" customHeight="1">
-      <c r="B46" s="4" t="s">
+      <c r="D56" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-    </row>
-    <row r="47" ht="4" customHeight="1"/>
-    <row r="48" ht="18" customHeight="1">
-      <c r="B48" s="13" t="s">
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="D48" s="13"/>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="B49" s="14" t="s">
+      <c r="C57" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="C49" s="14" t="s">
+      <c r="D57" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="D49" s="14"/>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="B50" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C50" s="15" t="s">
+    </row>
+    <row r="58" ht="32.4" customHeight="1">
+      <c r="B58" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="D50" s="15"/>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="B51" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C51" s="14" t="s">
+      <c r="C58" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="D51" s="14"/>
-    </row>
-    <row r="52" ht="6" customHeight="1"/>
-    <row r="53" ht="8" customHeight="1"/>
-    <row r="54" ht="24" customHeight="1">
-      <c r="B54" s="4" t="s">
+      <c r="D58" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-    </row>
-    <row r="55" ht="4" customHeight="1"/>
-    <row r="56" ht="18" customHeight="1">
-      <c r="B56" s="7" t="s">
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="B57" s="7" t="s">
+      <c r="C59" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="B58" s="7" t="s">
+      <c r="D59" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="B59" s="7" t="s">
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-    </row>
-    <row r="60" ht="6" customHeight="1"/>
+      <c r="C60" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="61" ht="46.8" customHeight="1">
+      <c r="B61" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1"/>
+    <row r="63" ht="8" customHeight="1"/>
+    <row r="64" ht="24" customHeight="1">
+      <c r="B64" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+    </row>
+    <row r="65" ht="4" customHeight="1"/>
+    <row r="66" ht="18" customHeight="1">
+      <c r="B66" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="D66" s="13"/>
+    </row>
+    <row r="67" ht="32.4" customHeight="1">
+      <c r="B67" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="D67" s="14"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="B68" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="D68" s="15"/>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="B69" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="C69" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="D69" s="14"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="B70" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="D70" s="15"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="B71" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C71" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="D71" s="14"/>
+    </row>
+    <row r="72" ht="6" customHeight="1"/>
+    <row r="73" ht="46.8" customHeight="1">
+      <c r="B73" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+    </row>
+    <row r="74" ht="6" customHeight="1"/>
+    <row r="75" ht="16.2" customHeight="1">
+      <c r="B75" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9"/>
+    </row>
+    <row r="76" ht="16.2" customHeight="1">
+      <c r="B76" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+    </row>
+    <row r="77" ht="6" customHeight="1"/>
+    <row r="78" ht="16.2" customHeight="1">
+      <c r="B78" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+    </row>
+    <row r="79" ht="16.2" customHeight="1">
+      <c r="B79" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+    </row>
+    <row r="80" ht="6" customHeight="1"/>
+    <row r="81" ht="8" customHeight="1"/>
+    <row r="82" ht="24" customHeight="1">
+      <c r="B82" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+    </row>
+    <row r="83" ht="4" customHeight="1"/>
+    <row r="84" ht="18" customHeight="1">
+      <c r="B84" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="B85" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="B86" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="B87" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+    </row>
+    <row r="88" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="50">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
@@ -6399,27 +6646,45 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B44:D44"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B87:D87"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -6457,7 +6722,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -6467,7 +6732,7 @@
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="7" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -6476,7 +6741,7 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="7" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -6486,489 +6751,489 @@
     <row r="7" ht="6" customHeight="1"/>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="13" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="14" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="15" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" ht="32.4" customHeight="1">
       <c r="B11" s="14" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="15" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="14" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>7</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="15" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>7</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" ht="32.4" customHeight="1">
       <c r="B15" s="14" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>7</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" ht="32.4" customHeight="1">
       <c r="B16" s="15" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" ht="32.4" customHeight="1">
       <c r="B17" s="14" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="15" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="14" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="14" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="15" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23" ht="46.8" customHeight="1">
       <c r="B23" s="14" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" ht="75.6" customHeight="1">
       <c r="B24" s="15" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" ht="61.2" customHeight="1">
       <c r="B25" s="14" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="15" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="14" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="15" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="14" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="15" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
     </row>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="14" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="15" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" ht="32.4" customHeight="1">
       <c r="B33" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="15" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>296</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="15" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>7</v>
@@ -6977,13 +7242,13 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>7</v>
@@ -6992,79 +7257,79 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="15" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="15" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="F41" s="14"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="15" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>7</v>
@@ -7073,421 +7338,421 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="F43" s="14"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="15" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
     </row>
     <row r="45" ht="32.4" customHeight="1">
       <c r="B45" s="14" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>331</v>
+        <v>356</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="15" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>333</v>
+        <v>358</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="14" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="F47" s="14"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="15" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="F48" s="15"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="14" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="15" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>343</v>
+        <v>368</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>345</v>
+        <v>370</v>
       </c>
     </row>
     <row r="51" ht="32.4" customHeight="1">
       <c r="B51" s="14" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>349</v>
+        <v>374</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="15" t="s">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
     </row>
     <row r="53" ht="32.4" customHeight="1">
       <c r="B53" s="14" t="s">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>357</v>
+        <v>382</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="15" t="s">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>358</v>
+        <v>383</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="14" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>363</v>
+        <v>388</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>364</v>
+        <v>389</v>
       </c>
     </row>
     <row r="56" ht="32.4" customHeight="1">
       <c r="B56" s="15" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>367</v>
+        <v>392</v>
       </c>
     </row>
     <row r="57" ht="32.4" customHeight="1">
       <c r="B57" s="14" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
     </row>
     <row r="58" ht="32.4" customHeight="1">
       <c r="B58" s="15" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="14" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="15" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="14" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="B62" s="15" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="B63" s="14" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="B64" s="15" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>393</v>
+        <v>418</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="B65" s="14" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="B66" s="15" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>398</v>
+        <v>423</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>401</v>
+        <v>426</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="B67" s="14" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
     </row>
     <row r="68" ht="6" customHeight="1"/>
@@ -7532,7 +7797,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -7541,16 +7806,16 @@
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>408</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" ht="32.4" customHeight="1">
@@ -7559,7 +7824,7 @@
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>7</v>
@@ -7567,207 +7832,207 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14" t="s">
-        <v>414</v>
+        <v>439</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" ht="32.4" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>422</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11" ht="32.4" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14" t="s">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="15" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="14" t="s">
-        <v>432</v>
+        <v>457</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>434</v>
+        <v>459</v>
       </c>
     </row>
     <row r="15" ht="32.4" customHeight="1">
       <c r="B15" s="15" t="s">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
     </row>
     <row r="16" ht="32.4" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="14" t="s">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>439</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15" t="s">
-        <v>441</v>
+        <v>466</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>442</v>
+        <v>467</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>443</v>
+        <v>468</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="14" t="s">
-        <v>444</v>
+        <v>469</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="15" t="s">
-        <v>447</v>
+        <v>472</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>448</v>
+        <v>473</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="14" t="s">
-        <v>449</v>
+        <v>474</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14" t="s">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="15" t="s">
-        <v>452</v>
+        <v>477</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
     </row>
     <row r="22" ht="32.4" customHeight="1">
       <c r="B22" s="14" t="s">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14" t="s">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="15" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="E23" s="15"/>
     </row>
@@ -7775,7 +8040,7 @@
     <row r="25" ht="8" customHeight="1"/>
     <row r="26" ht="24" customHeight="1">
       <c r="B26" s="4" t="s">
-        <v>459</v>
+        <v>484</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -7784,7 +8049,7 @@
     <row r="27" ht="4" customHeight="1"/>
     <row r="28" ht="32.4" customHeight="1">
       <c r="B28" s="7" t="s">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -7792,7 +8057,7 @@
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="7" t="s">
-        <v>461</v>
+        <v>486</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -7800,7 +8065,7 @@
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="7" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -7808,7 +8073,7 @@
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="7" t="s">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -7816,7 +8081,7 @@
     </row>
     <row r="32" ht="32.4" customHeight="1">
       <c r="B32" s="7" t="s">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -7824,7 +8089,7 @@
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="7" t="s">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -7832,7 +8097,7 @@
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="7" t="s">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -7842,7 +8107,7 @@
     <row r="36" ht="8" customHeight="1"/>
     <row r="37" ht="24" customHeight="1">
       <c r="B37" s="4" t="s">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -7851,61 +8116,61 @@
     <row r="38" ht="4" customHeight="1"/>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="13" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>469</v>
+        <v>494</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="E39" s="13"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="14" t="s">
-        <v>471</v>
+        <v>496</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>472</v>
+        <v>497</v>
       </c>
       <c r="E40" s="14"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="15" t="s">
-        <v>473</v>
+        <v>498</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>474</v>
+        <v>499</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="E41" s="15"/>
     </row>
     <row r="42" ht="32.4" customHeight="1">
       <c r="B42" s="14" t="s">
-        <v>476</v>
+        <v>501</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>477</v>
+        <v>502</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>478</v>
+        <v>503</v>
       </c>
       <c r="E42" s="14"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="15" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="E43" s="15"/>
     </row>
@@ -7963,7 +8228,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -7972,7 +8237,7 @@
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="16.2" customHeight="1">
       <c r="B5" s="9" t="s">
-        <v>483</v>
+        <v>508</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -7980,7 +8245,7 @@
     </row>
     <row r="6" ht="16.2" customHeight="1">
       <c r="B6" s="10" t="s">
-        <v>484</v>
+        <v>509</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -7988,7 +8253,7 @@
     </row>
     <row r="7" ht="16.2" customHeight="1">
       <c r="B7" s="10" t="s">
-        <v>485</v>
+        <v>510</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -7996,7 +8261,7 @@
     </row>
     <row r="8" ht="16.2" customHeight="1">
       <c r="B8" s="10" t="s">
-        <v>486</v>
+        <v>511</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
@@ -8004,7 +8269,7 @@
     </row>
     <row r="9" ht="16.2" customHeight="1">
       <c r="B9" s="10" t="s">
-        <v>487</v>
+        <v>512</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
@@ -8012,7 +8277,7 @@
     </row>
     <row r="10" ht="16.2" customHeight="1">
       <c r="B10" s="10" t="s">
-        <v>488</v>
+        <v>513</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -8020,7 +8285,7 @@
     </row>
     <row r="11" ht="16.2" customHeight="1">
       <c r="B11" s="10" t="s">
-        <v>489</v>
+        <v>514</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
@@ -8028,7 +8293,7 @@
     </row>
     <row r="12" ht="16.2" customHeight="1">
       <c r="B12" s="10" t="s">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -8036,7 +8301,7 @@
     </row>
     <row r="13" ht="16.2" customHeight="1">
       <c r="B13" s="10" t="s">
-        <v>491</v>
+        <v>516</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -8044,7 +8309,7 @@
     </row>
     <row r="14" ht="16.2" customHeight="1">
       <c r="B14" s="10" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
@@ -8052,7 +8317,7 @@
     </row>
     <row r="15" ht="16.2" customHeight="1">
       <c r="B15" s="10" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
@@ -8060,7 +8325,7 @@
     </row>
     <row r="16" ht="16.2" customHeight="1">
       <c r="B16" s="10" t="s">
-        <v>494</v>
+        <v>519</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -8068,7 +8333,7 @@
     </row>
     <row r="17" ht="16.2" customHeight="1">
       <c r="B17" s="10" t="s">
-        <v>495</v>
+        <v>520</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -8076,7 +8341,7 @@
     </row>
     <row r="18" ht="16.2" customHeight="1">
       <c r="B18" s="10" t="s">
-        <v>496</v>
+        <v>521</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -8084,7 +8349,7 @@
     </row>
     <row r="19" ht="16.2" customHeight="1">
       <c r="B19" s="10" t="s">
-        <v>497</v>
+        <v>522</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -8092,7 +8357,7 @@
     </row>
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="10" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -8100,7 +8365,7 @@
     </row>
     <row r="21" ht="16.2" customHeight="1">
       <c r="B21" s="10" t="s">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -8108,7 +8373,7 @@
     </row>
     <row r="22" ht="16.2" customHeight="1">
       <c r="B22" s="10" t="s">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
@@ -8116,7 +8381,7 @@
     </row>
     <row r="23" ht="16.2" customHeight="1">
       <c r="B23" s="10" t="s">
-        <v>501</v>
+        <v>526</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
@@ -8124,7 +8389,7 @@
     </row>
     <row r="24" ht="16.2" customHeight="1">
       <c r="B24" s="10" t="s">
-        <v>502</v>
+        <v>527</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
@@ -8132,7 +8397,7 @@
     </row>
     <row r="25" ht="16.2" customHeight="1">
       <c r="B25" s="10" t="s">
-        <v>503</v>
+        <v>528</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
@@ -8140,7 +8405,7 @@
     </row>
     <row r="26" ht="16.2" customHeight="1">
       <c r="B26" s="10" t="s">
-        <v>504</v>
+        <v>529</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
@@ -8148,7 +8413,7 @@
     </row>
     <row r="27" ht="16.2" customHeight="1">
       <c r="B27" s="10" t="s">
-        <v>505</v>
+        <v>530</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
@@ -8156,7 +8421,7 @@
     </row>
     <row r="28" ht="16.2" customHeight="1">
       <c r="B28" s="10" t="s">
-        <v>506</v>
+        <v>531</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
@@ -8164,7 +8429,7 @@
     </row>
     <row r="29" ht="16.2" customHeight="1">
       <c r="B29" s="10" t="s">
-        <v>507</v>
+        <v>532</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
@@ -8172,7 +8437,7 @@
     </row>
     <row r="30" ht="16.2" customHeight="1">
       <c r="B30" s="10" t="s">
-        <v>508</v>
+        <v>533</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
@@ -8180,7 +8445,7 @@
     </row>
     <row r="31" ht="16.2" customHeight="1">
       <c r="B31" s="10" t="s">
-        <v>509</v>
+        <v>534</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="10"/>
@@ -8188,7 +8453,7 @@
     </row>
     <row r="32" ht="16.2" customHeight="1">
       <c r="B32" s="10" t="s">
-        <v>510</v>
+        <v>535</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -8196,7 +8461,7 @@
     </row>
     <row r="33" ht="16.2" customHeight="1">
       <c r="B33" s="10" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -8204,7 +8469,7 @@
     </row>
     <row r="34" ht="16.2" customHeight="1">
       <c r="B34" s="10" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
@@ -8212,7 +8477,7 @@
     </row>
     <row r="35" ht="16.2" customHeight="1">
       <c r="B35" s="10" t="s">
-        <v>513</v>
+        <v>538</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
@@ -8220,7 +8485,7 @@
     </row>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="10" t="s">
-        <v>514</v>
+        <v>539</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
@@ -8228,7 +8493,7 @@
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>515</v>
+        <v>540</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
@@ -8236,7 +8501,7 @@
     </row>
     <row r="38" ht="16.2" customHeight="1">
       <c r="B38" s="10" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
@@ -8244,7 +8509,7 @@
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>517</v>
+        <v>542</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
@@ -8252,7 +8517,7 @@
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="11" t="s">
-        <v>518</v>
+        <v>543</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
@@ -8262,7 +8527,7 @@
     <row r="42" ht="8" customHeight="1"/>
     <row r="43" ht="24" customHeight="1">
       <c r="B43" s="4" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -8271,401 +8536,401 @@
     <row r="44" ht="4" customHeight="1"/>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="13" t="s">
-        <v>520</v>
+        <v>545</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>521</v>
+        <v>546</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>523</v>
+        <v>548</v>
       </c>
     </row>
     <row r="46" ht="32.4" customHeight="1">
       <c r="B46" s="14" t="s">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>526</v>
+        <v>551</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>527</v>
+        <v>552</v>
       </c>
     </row>
     <row r="47" ht="32.4" customHeight="1">
       <c r="B47" s="15" t="s">
-        <v>528</v>
+        <v>553</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>529</v>
+        <v>554</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>530</v>
+        <v>555</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>531</v>
+        <v>556</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="14" t="s">
-        <v>532</v>
+        <v>557</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>533</v>
+        <v>558</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>534</v>
+        <v>559</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>535</v>
+        <v>560</v>
       </c>
     </row>
     <row r="49" ht="32.4" customHeight="1">
       <c r="B49" s="15" t="s">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>537</v>
+        <v>562</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>538</v>
+        <v>563</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>539</v>
+        <v>564</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="14" t="s">
-        <v>540</v>
+        <v>565</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>543</v>
+        <v>568</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="15" t="s">
-        <v>544</v>
+        <v>569</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>545</v>
+        <v>570</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>546</v>
+        <v>571</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>547</v>
+        <v>572</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="14" t="s">
-        <v>548</v>
+        <v>573</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>545</v>
+        <v>570</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>549</v>
+        <v>574</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>550</v>
+        <v>575</v>
       </c>
     </row>
     <row r="53" ht="32.4" customHeight="1">
       <c r="B53" s="15" t="s">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>552</v>
+        <v>577</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>553</v>
+        <v>578</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="14" t="s">
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>556</v>
+        <v>581</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>557</v>
+        <v>582</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>558</v>
+        <v>583</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="15" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>561</v>
+        <v>586</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>562</v>
+        <v>587</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="14" t="s">
-        <v>563</v>
+        <v>588</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>565</v>
+        <v>590</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>566</v>
+        <v>591</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="15" t="s">
-        <v>567</v>
+        <v>592</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>569</v>
+        <v>594</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>570</v>
+        <v>595</v>
       </c>
     </row>
     <row r="58" ht="32.4" customHeight="1">
       <c r="B58" s="14" t="s">
-        <v>571</v>
+        <v>596</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>573</v>
+        <v>598</v>
       </c>
     </row>
     <row r="59" ht="32.4" customHeight="1">
       <c r="B59" s="15" t="s">
-        <v>574</v>
+        <v>599</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>576</v>
+        <v>601</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>573</v>
+        <v>598</v>
       </c>
     </row>
     <row r="60" ht="32.4" customHeight="1">
       <c r="B60" s="14" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="15" t="s">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>582</v>
+        <v>607</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>583</v>
+        <v>608</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>584</v>
+        <v>609</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="B62" s="14" t="s">
-        <v>585</v>
+        <v>610</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>533</v>
+        <v>558</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>586</v>
+        <v>611</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>587</v>
+        <v>612</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="B63" s="15" t="s">
-        <v>588</v>
+        <v>613</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>589</v>
+        <v>614</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>590</v>
+        <v>615</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
     </row>
     <row r="64" ht="32.4" customHeight="1">
       <c r="B64" s="14" t="s">
-        <v>592</v>
+        <v>617</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>593</v>
+        <v>618</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>594</v>
+        <v>619</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>595</v>
+        <v>620</v>
       </c>
     </row>
     <row r="65" ht="32.4" customHeight="1">
       <c r="B65" s="15" t="s">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>597</v>
+        <v>622</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>598</v>
+        <v>623</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>599</v>
+        <v>624</v>
       </c>
     </row>
     <row r="66" ht="32.4" customHeight="1">
       <c r="B66" s="14" t="s">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>601</v>
+        <v>626</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>602</v>
+        <v>627</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>603</v>
+        <v>628</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="B67" s="15" t="s">
-        <v>604</v>
+        <v>629</v>
       </c>
       <c r="C67" s="15" t="s">
+        <v>630</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>631</v>
+      </c>
+      <c r="E67" s="15" t="s">
         <v>605</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>606</v>
-      </c>
-      <c r="E67" s="15" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="68" ht="32.4" customHeight="1">
       <c r="B68" s="14" t="s">
-        <v>607</v>
+        <v>632</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>608</v>
+        <v>633</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>609</v>
+        <v>634</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>610</v>
+        <v>635</v>
       </c>
     </row>
     <row r="69" ht="32.4" customHeight="1">
       <c r="B69" s="15" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>612</v>
+        <v>637</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>613</v>
+        <v>638</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>614</v>
+        <v>639</v>
       </c>
     </row>
     <row r="70" ht="32.4" customHeight="1">
       <c r="B70" s="14" t="s">
-        <v>615</v>
+        <v>640</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>616</v>
+        <v>641</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>617</v>
+        <v>642</v>
       </c>
     </row>
     <row r="71" ht="32.4" customHeight="1">
       <c r="B71" s="15" t="s">
-        <v>618</v>
+        <v>643</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>616</v>
+        <v>641</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>619</v>
+        <v>644</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>620</v>
+        <v>645</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="B72" s="14" t="s">
-        <v>621</v>
+        <v>646</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>622</v>
+        <v>647</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>623</v>
+        <v>648</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>624</v>
+        <v>649</v>
       </c>
     </row>
     <row r="73" ht="6" customHeight="1"/>
     <row r="74" ht="8" customHeight="1"/>
     <row r="75" ht="24" customHeight="1">
       <c r="B75" s="4" t="s">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -8674,133 +8939,133 @@
     <row r="76" ht="4" customHeight="1"/>
     <row r="77" ht="18" customHeight="1">
       <c r="B77" s="13" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>626</v>
+        <v>651</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>627</v>
+        <v>652</v>
       </c>
       <c r="E77" s="13"/>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="B78" s="14" t="s">
-        <v>628</v>
+        <v>653</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>629</v>
+        <v>654</v>
       </c>
       <c r="E78" s="14"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="B79" s="15" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>630</v>
+        <v>655</v>
       </c>
       <c r="E79" s="15"/>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="B80" s="14" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>631</v>
+        <v>656</v>
       </c>
       <c r="E80" s="14"/>
     </row>
     <row r="81" ht="32.4" customHeight="1">
       <c r="B81" s="15" t="s">
-        <v>632</v>
+        <v>657</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>563</v>
+        <v>588</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>633</v>
+        <v>658</v>
       </c>
       <c r="E81" s="15"/>
     </row>
     <row r="82" ht="32.4" customHeight="1">
       <c r="B82" s="14" t="s">
-        <v>634</v>
+        <v>659</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>567</v>
+        <v>592</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>635</v>
+        <v>660</v>
       </c>
       <c r="E82" s="14"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="B83" s="15" t="s">
-        <v>636</v>
+        <v>661</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>571</v>
+        <v>596</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>637</v>
+        <v>662</v>
       </c>
       <c r="E83" s="15"/>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="B84" s="14" t="s">
-        <v>638</v>
+        <v>663</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>639</v>
+        <v>664</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>640</v>
+        <v>665</v>
       </c>
       <c r="E84" s="14"/>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="B85" s="15" t="s">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>642</v>
+        <v>667</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>643</v>
+        <v>668</v>
       </c>
       <c r="E85" s="15"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="B86" s="14" t="s">
-        <v>644</v>
+        <v>669</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="E86" s="14"/>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="B87" s="15" t="s">
-        <v>647</v>
+        <v>672</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>648</v>
+        <v>673</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>649</v>
+        <v>674</v>
       </c>
       <c r="E87" s="15"/>
     </row>
@@ -8808,7 +9073,7 @@
     <row r="89" ht="8" customHeight="1"/>
     <row r="90" ht="24" customHeight="1">
       <c r="B90" s="4" t="s">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -8817,7 +9082,7 @@
     <row r="91" ht="4" customHeight="1"/>
     <row r="92" ht="18" customHeight="1">
       <c r="B92" s="7" t="s">
-        <v>651</v>
+        <v>676</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
@@ -8825,7 +9090,7 @@
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="B93" s="7" t="s">
-        <v>652</v>
+        <v>677</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
@@ -8833,7 +9098,7 @@
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="B94" s="7" t="s">
-        <v>653</v>
+        <v>678</v>
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
@@ -8841,7 +9106,7 @@
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="B95" s="7" t="s">
-        <v>654</v>
+        <v>679</v>
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
@@ -8939,7 +9204,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>655</v>
+        <v>680</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -8947,42 +9212,42 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>656</v>
+        <v>681</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>659</v>
+        <v>684</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>660</v>
+        <v>685</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>661</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>662</v>
+        <v>687</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>663</v>
+        <v>688</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>664</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8" ht="6" customHeight="1"/>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="24" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>665</v>
+        <v>690</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -8990,7 +9255,7 @@
     <row r="11" ht="4" customHeight="1"/>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="6" t="s">
-        <v>666</v>
+        <v>691</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -8998,49 +9263,49 @@
     <row r="13" ht="6" customHeight="1"/>
     <row r="14" ht="16.2" customHeight="1">
       <c r="B14" s="9" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
     </row>
     <row r="15" ht="16.2" customHeight="1">
       <c r="B15" s="10" t="s">
-        <v>667</v>
+        <v>692</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
     </row>
     <row r="16" ht="16.2" customHeight="1">
       <c r="B16" s="10" t="s">
-        <v>668</v>
+        <v>693</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
     </row>
     <row r="17" ht="16.2" customHeight="1">
       <c r="B17" s="10" t="s">
-        <v>669</v>
+        <v>694</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
     </row>
     <row r="18" ht="16.2" customHeight="1">
       <c r="B18" s="10" t="s">
-        <v>670</v>
+        <v>695</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
     </row>
     <row r="19" ht="16.2" customHeight="1">
       <c r="B19" s="10" t="s">
-        <v>671</v>
+        <v>696</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
     </row>
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="11" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -9048,28 +9313,28 @@
     <row r="21" ht="6" customHeight="1"/>
     <row r="22" ht="16.2" customHeight="1">
       <c r="B22" s="9" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
     </row>
     <row r="23" ht="16.2" customHeight="1">
       <c r="B23" s="10" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
     </row>
     <row r="24" ht="16.2" customHeight="1">
       <c r="B24" s="10" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
     </row>
     <row r="25" ht="16.2" customHeight="1">
       <c r="B25" s="11" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
@@ -9077,141 +9342,141 @@
     <row r="26" ht="6" customHeight="1"/>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="13" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="14" t="s">
-        <v>676</v>
+        <v>196</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>677</v>
+        <v>197</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>678</v>
+        <v>701</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>679</v>
+        <v>702</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>680</v>
+        <v>703</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>681</v>
+        <v>704</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="14" t="s">
-        <v>682</v>
+        <v>705</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>683</v>
+        <v>706</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>684</v>
+        <v>707</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="15" t="s">
-        <v>685</v>
+        <v>708</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>686</v>
+        <v>709</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>687</v>
+        <v>710</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="14" t="s">
-        <v>688</v>
+        <v>711</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>689</v>
+        <v>712</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>690</v>
+        <v>713</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="15" t="s">
-        <v>691</v>
+        <v>714</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>692</v>
+        <v>715</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>693</v>
+        <v>716</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="14" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>694</v>
+        <v>717</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="15" t="s">
-        <v>695</v>
+        <v>718</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>696</v>
+        <v>719</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>697</v>
+        <v>720</v>
       </c>
     </row>
     <row r="36" ht="32.4" customHeight="1">
       <c r="B36" s="14" t="s">
-        <v>698</v>
+        <v>721</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>699</v>
+        <v>722</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>700</v>
+        <v>723</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="15" t="s">
-        <v>701</v>
+        <v>724</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>702</v>
+        <v>725</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>703</v>
+        <v>726</v>
       </c>
     </row>
     <row r="38" ht="32.4" customHeight="1">
       <c r="B38" s="14" t="s">
-        <v>704</v>
+        <v>727</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>705</v>
+        <v>728</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>706</v>
+        <v>729</v>
       </c>
     </row>
     <row r="39" ht="6" customHeight="1"/>
     <row r="40" ht="8" customHeight="1"/>
     <row r="41" ht="24" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>707</v>
+        <v>730</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -9219,163 +9484,163 @@
     <row r="42" ht="4" customHeight="1"/>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="13" t="s">
-        <v>708</v>
+        <v>731</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="14" t="s">
-        <v>709</v>
+        <v>732</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>710</v>
+        <v>733</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>711</v>
+        <v>734</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="15" t="s">
-        <v>712</v>
+        <v>735</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>713</v>
+        <v>736</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>714</v>
+        <v>737</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="14" t="s">
-        <v>715</v>
+        <v>738</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>716</v>
+        <v>739</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>717</v>
+        <v>740</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="15" t="s">
-        <v>718</v>
+        <v>741</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>719</v>
+        <v>742</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>720</v>
+        <v>743</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="14" t="s">
-        <v>721</v>
+        <v>744</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>722</v>
+        <v>745</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>723</v>
+        <v>746</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="15" t="s">
-        <v>628</v>
+        <v>653</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>725</v>
+        <v>748</v>
       </c>
     </row>
     <row r="50" ht="32.4" customHeight="1">
       <c r="B50" s="14" t="s">
-        <v>726</v>
+        <v>749</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>727</v>
+        <v>750</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>728</v>
+        <v>751</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="15" t="s">
-        <v>729</v>
+        <v>752</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>730</v>
+        <v>753</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="14" t="s">
-        <v>731</v>
+        <v>754</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>732</v>
+        <v>755</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>733</v>
+        <v>756</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="15" t="s">
-        <v>734</v>
+        <v>757</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>735</v>
+        <v>758</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="14" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>737</v>
+        <v>760</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="15" t="s">
-        <v>738</v>
+        <v>761</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>739</v>
+        <v>762</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="14" t="s">
-        <v>740</v>
+        <v>763</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>741</v>
+        <v>764</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>742</v>
+        <v>765</v>
       </c>
     </row>
     <row r="57" ht="6" customHeight="1"/>
     <row r="58" ht="8" customHeight="1"/>
     <row r="59" ht="24" customHeight="1">
       <c r="B59" s="4" t="s">
-        <v>743</v>
+        <v>766</v>
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
@@ -9383,21 +9648,21 @@
     <row r="60" ht="4" customHeight="1"/>
     <row r="61" ht="16.2" customHeight="1">
       <c r="B61" s="9" t="s">
-        <v>744</v>
+        <v>767</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
     </row>
     <row r="62" ht="16.2" customHeight="1">
       <c r="B62" s="10" t="s">
-        <v>745</v>
+        <v>768</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
     </row>
     <row r="63" ht="16.2" customHeight="1">
       <c r="B63" s="11" t="s">
-        <v>746</v>
+        <v>769</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
@@ -9405,14 +9670,14 @@
     <row r="64" ht="6" customHeight="1"/>
     <row r="65" ht="16.2" customHeight="1">
       <c r="B65" s="9" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
     </row>
     <row r="66" ht="30.6" customHeight="1">
       <c r="B66" s="11" t="s">
-        <v>747</v>
+        <v>770</v>
       </c>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
@@ -9420,14 +9685,14 @@
     <row r="67" ht="6" customHeight="1"/>
     <row r="68" ht="18" customHeight="1">
       <c r="B68" s="7" t="s">
-        <v>748</v>
+        <v>771</v>
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="B69" s="7" t="s">
-        <v>749</v>
+        <v>772</v>
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
@@ -9436,7 +9701,7 @@
     <row r="71" ht="8" customHeight="1"/>
     <row r="72" ht="24" customHeight="1">
       <c r="B72" s="4" t="s">
-        <v>750</v>
+        <v>773</v>
       </c>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -9444,21 +9709,21 @@
     <row r="73" ht="4" customHeight="1"/>
     <row r="74" ht="18" customHeight="1">
       <c r="B74" s="7" t="s">
-        <v>751</v>
+        <v>774</v>
       </c>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="B75" s="7" t="s">
-        <v>752</v>
+        <v>775</v>
       </c>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="B76" s="7" t="s">
-        <v>753</v>
+        <v>776</v>
       </c>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
@@ -9527,7 +9792,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>754</v>
+        <v>777</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -9535,7 +9800,7 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="6" t="s">
-        <v>755</v>
+        <v>778</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -9543,75 +9808,75 @@
     <row r="6" ht="6" customHeight="1"/>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="13" t="s">
-        <v>756</v>
+        <v>779</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>757</v>
+        <v>780</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>758</v>
+        <v>781</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>759</v>
+        <v>782</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>760</v>
+        <v>783</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>761</v>
+        <v>784</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>762</v>
+        <v>785</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>763</v>
+        <v>786</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>764</v>
+        <v>787</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>765</v>
+        <v>788</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>766</v>
+        <v>789</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>767</v>
+        <v>790</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>768</v>
+        <v>791</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>769</v>
+        <v>792</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>770</v>
+        <v>793</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>771</v>
+        <v>794</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>772</v>
+        <v>795</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>773</v>
+        <v>796</v>
       </c>
     </row>
     <row r="13" ht="6" customHeight="1"/>
     <row r="14" ht="8" customHeight="1"/>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>774</v>
+        <v>797</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -9619,49 +9884,49 @@
     <row r="16" ht="4" customHeight="1"/>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="7" t="s">
-        <v>775</v>
+        <v>798</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="7" t="s">
-        <v>776</v>
+        <v>799</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="7" t="s">
-        <v>777</v>
+        <v>800</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="7" t="s">
-        <v>778</v>
+        <v>801</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="7" t="s">
-        <v>779</v>
+        <v>802</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="7" t="s">
-        <v>780</v>
+        <v>803</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="7" t="s">
-        <v>781</v>
+        <v>804</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -9670,7 +9935,7 @@
     <row r="25" ht="8" customHeight="1"/>
     <row r="26" ht="24" customHeight="1">
       <c r="B26" s="4" t="s">
-        <v>782</v>
+        <v>805</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -9678,53 +9943,53 @@
     <row r="27" ht="4" customHeight="1"/>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="13" t="s">
-        <v>783</v>
+        <v>806</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>784</v>
+        <v>807</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>785</v>
+        <v>808</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="14" t="s">
-        <v>786</v>
+        <v>809</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>787</v>
+        <v>810</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>788</v>
+        <v>811</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="15" t="s">
-        <v>789</v>
+        <v>812</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>790</v>
+        <v>813</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>791</v>
+        <v>814</v>
       </c>
     </row>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="14" t="s">
-        <v>792</v>
+        <v>815</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>793</v>
+        <v>816</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>794</v>
+        <v>817</v>
       </c>
     </row>
     <row r="32" ht="6" customHeight="1"/>
     <row r="33" ht="8" customHeight="1"/>
     <row r="34" ht="24" customHeight="1">
       <c r="B34" s="4" t="s">
-        <v>795</v>
+        <v>818</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -9732,35 +9997,35 @@
     <row r="35" ht="4" customHeight="1"/>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="9" t="s">
-        <v>796</v>
+        <v>819</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>797</v>
+        <v>820</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="16.2" customHeight="1">
       <c r="B38" s="10" t="s">
-        <v>798</v>
+        <v>821</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>799</v>
+        <v>822</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="11" t="s">
-        <v>800</v>
+        <v>823</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
@@ -9769,7 +10034,7 @@
     <row r="42" ht="8" customHeight="1"/>
     <row r="43" ht="24" customHeight="1">
       <c r="B43" s="4" t="s">
-        <v>801</v>
+        <v>824</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -9777,21 +10042,21 @@
     <row r="44" ht="4" customHeight="1"/>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="7" t="s">
-        <v>802</v>
+        <v>825</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="7" t="s">
-        <v>803</v>
+        <v>826</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="7" t="s">
-        <v>804</v>
+        <v>827</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -9800,7 +10065,7 @@
     <row r="49" ht="8" customHeight="1"/>
     <row r="50" ht="24" customHeight="1">
       <c r="B50" s="4" t="s">
-        <v>805</v>
+        <v>828</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -9808,7 +10073,7 @@
     <row r="51" ht="4" customHeight="1"/>
     <row r="52" ht="46.8" customHeight="1">
       <c r="B52" s="6" t="s">
-        <v>806</v>
+        <v>829</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
